--- a/Tools/languages.xlsx
+++ b/Tools/languages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/projects/hieunm/chess/Tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F69411-D919-9241-BAED-07D58ADC8E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518B613D-4ABD-0E4B-8A90-3565CEFBA5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15840" xr2:uid="{E6764379-1D78-984F-8202-F6CD8653F853}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>Key</t>
   </si>
@@ -122,13 +122,22 @@
     <t>Lịch sử</t>
   </si>
   <si>
-    <t>page.home</t>
-  </si>
-  <si>
-    <t>page.history</t>
-  </si>
-  <si>
-    <t>page.about</t>
+    <t>page.home.title</t>
+  </si>
+  <si>
+    <t>page.history.title</t>
+  </si>
+  <si>
+    <t>page.about.title</t>
+  </si>
+  <si>
+    <t>home.turn.title</t>
+  </si>
+  <si>
+    <t>Turn</t>
+  </si>
+  <si>
+    <t>Lượt đánh</t>
   </si>
 </sst>
 </file>
@@ -695,10 +704,16 @@
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+    <row r="16" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>

--- a/Tools/languages.xlsx
+++ b/Tools/languages.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/projects/hieunm/chess/Tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518B613D-4ABD-0E4B-8A90-3565CEFBA5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3D9696-AA85-D14D-B265-6F0B144E45C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15840" xr2:uid="{E6764379-1D78-984F-8202-F6CD8653F853}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>Key</t>
   </si>
@@ -98,9 +98,6 @@
     <t>menu.home</t>
   </si>
   <si>
-    <t>menu.about</t>
-  </si>
-  <si>
     <t>Home</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
     <t>Thông tin</t>
   </si>
   <si>
-    <t>menu.history</t>
-  </si>
-  <si>
     <t>History</t>
   </si>
   <si>
@@ -138,6 +132,15 @@
   </si>
   <si>
     <t>Lượt đánh</t>
+  </si>
+  <si>
+    <t>menu.logout</t>
+  </si>
+  <si>
+    <t>Logout</t>
+  </si>
+  <si>
+    <t>Đăng xuất</t>
   </si>
 </sst>
 </file>
@@ -543,7 +546,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A972E6DD-A464-F34F-8D77-960075701A8D}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C473"/>
+  <dimension ref="A1:C472"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.5" style="2" bestFit="1" customWidth="1"/>
@@ -575,35 +578,35 @@
     </row>
     <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.2">
@@ -622,98 +625,92 @@
         <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>33</v>
-      </c>
+    </row>
+    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
@@ -1146,7 +1143,7 @@
       <c r="C102" s="3"/>
     </row>
     <row r="103" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A103" s="1"/>
+      <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
     </row>
@@ -1156,7 +1153,7 @@
       <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A105" s="3"/>
+      <c r="A105" s="1"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
     </row>
@@ -1487,8 +1484,8 @@
     </row>
     <row r="171" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
-      <c r="B171" s="3"/>
-      <c r="C171" s="3"/>
+      <c r="B171" s="4"/>
+      <c r="C171" s="4"/>
     </row>
     <row r="172" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
@@ -1512,8 +1509,8 @@
     </row>
     <row r="176" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
-      <c r="B176" s="4"/>
-      <c r="C176" s="4"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
     </row>
     <row r="177" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
@@ -1552,8 +1549,8 @@
     </row>
     <row r="184" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
-      <c r="B184" s="3"/>
-      <c r="C184" s="3"/>
+      <c r="B184" s="4"/>
+      <c r="C184" s="4"/>
     </row>
     <row r="185" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
@@ -1577,8 +1574,8 @@
     </row>
     <row r="189" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
-      <c r="B189" s="4"/>
-      <c r="C189" s="4"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
     </row>
     <row r="190" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
@@ -2272,12 +2269,12 @@
     </row>
     <row r="328" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
-      <c r="B328" s="3"/>
+      <c r="B328" s="1"/>
       <c r="C328" s="3"/>
     </row>
     <row r="329" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
-      <c r="B329" s="1"/>
+      <c r="B329" s="3"/>
       <c r="C329" s="3"/>
     </row>
     <row r="330" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2447,7 +2444,7 @@
     </row>
     <row r="363" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A363" s="1"/>
-      <c r="B363" s="3"/>
+      <c r="B363" s="1"/>
       <c r="C363" s="3"/>
     </row>
     <row r="364" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2457,7 +2454,7 @@
     </row>
     <row r="365" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A365" s="1"/>
-      <c r="B365" s="1"/>
+      <c r="B365" s="3"/>
       <c r="C365" s="3"/>
     </row>
     <row r="366" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2822,13 +2819,13 @@
     </row>
     <row r="438" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A438" s="1"/>
-      <c r="B438" s="3"/>
-      <c r="C438" s="3"/>
+      <c r="B438" s="1"/>
+      <c r="C438" s="1"/>
     </row>
     <row r="439" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A439" s="1"/>
-      <c r="B439" s="1"/>
-      <c r="C439" s="1"/>
+      <c r="B439" s="3"/>
+      <c r="C439" s="3"/>
     </row>
     <row r="440" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A440" s="1"/>
@@ -2887,8 +2884,8 @@
     </row>
     <row r="451" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A451" s="1"/>
-      <c r="B451" s="3"/>
-      <c r="C451" s="3"/>
+      <c r="B451" s="1"/>
+      <c r="C451" s="1"/>
     </row>
     <row r="452" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A452" s="1"/>
@@ -2912,8 +2909,8 @@
     </row>
     <row r="456" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A456" s="1"/>
-      <c r="B456" s="1"/>
-      <c r="C456" s="1"/>
+      <c r="B456" s="3"/>
+      <c r="C456" s="3"/>
     </row>
     <row r="457" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A457" s="1"/>
@@ -2987,22 +2984,17 @@
     </row>
     <row r="471" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A471" s="1"/>
-      <c r="B471" s="3"/>
-      <c r="C471" s="3"/>
+      <c r="B471" s="1"/>
+      <c r="C471" s="1"/>
     </row>
     <row r="472" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
     </row>
-    <row r="473" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A473" s="1"/>
-      <c r="B473" s="1"/>
-      <c r="C473" s="1"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A280:C284">
-    <sortCondition ref="A280:A284"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A279:C283">
+    <sortCondition ref="A279:A283"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tools/languages.xlsx
+++ b/Tools/languages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/projects/hieunm/chess/Tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3D9696-AA85-D14D-B265-6F0B144E45C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46057BD-896D-9347-B9EC-C00727019DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15840" xr2:uid="{E6764379-1D78-984F-8202-F6CD8653F853}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>Key</t>
   </si>
@@ -47,15 +47,6 @@
     <t>Vietnamese</t>
   </si>
   <si>
-    <t>This field is required</t>
-  </si>
-  <si>
-    <t>Trường này bắt buộc nhập</t>
-  </si>
-  <si>
-    <t>constant.field-required</t>
-  </si>
-  <si>
     <t>settings.header</t>
   </si>
   <si>
@@ -141,6 +132,33 @@
   </si>
   <si>
     <t>Đăng xuất</t>
+  </si>
+  <si>
+    <t>Chess game</t>
+  </si>
+  <si>
+    <t>Cờ vua</t>
+  </si>
+  <si>
+    <t>menu.app-name</t>
+  </si>
+  <si>
+    <t>menu.users</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>Người dùng</t>
+  </si>
+  <si>
+    <t>Analytic</t>
+  </si>
+  <si>
+    <t>Phân tích</t>
+  </si>
+  <si>
+    <t>menu.analytics</t>
   </si>
 </sst>
 </file>
@@ -546,7 +564,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A972E6DD-A464-F34F-8D77-960075701A8D}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C472"/>
+  <dimension ref="A1:C474"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.5" style="2" bestFit="1" customWidth="1"/>
@@ -567,21 +585,21 @@
     </row>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>22</v>
@@ -589,122 +607,128 @@
     </row>
     <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="15" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -712,10 +736,16 @@
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+    <row r="17" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
@@ -1143,22 +1173,22 @@
       <c r="C102" s="3"/>
     </row>
     <row r="103" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A103" s="3"/>
+      <c r="A103" s="1"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
     </row>
     <row r="104" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A104" s="3"/>
+      <c r="A104" s="1"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A105" s="1"/>
+      <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
     </row>
     <row r="106" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A106" s="1"/>
+      <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
     </row>
@@ -1484,13 +1514,13 @@
     </row>
     <row r="171" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
-      <c r="B171" s="4"/>
-      <c r="C171" s="4"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
     </row>
     <row r="172" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
-      <c r="B172" s="4"/>
-      <c r="C172" s="4"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
     </row>
     <row r="173" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
@@ -1509,13 +1539,13 @@
     </row>
     <row r="176" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
-      <c r="B176" s="3"/>
-      <c r="C176" s="3"/>
+      <c r="B176" s="4"/>
+      <c r="C176" s="4"/>
     </row>
     <row r="177" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
-      <c r="B177" s="3"/>
-      <c r="C177" s="3"/>
+      <c r="B177" s="4"/>
+      <c r="C177" s="4"/>
     </row>
     <row r="178" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
@@ -1549,13 +1579,13 @@
     </row>
     <row r="184" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
-      <c r="B184" s="4"/>
-      <c r="C184" s="4"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
     </row>
     <row r="185" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
-      <c r="B185" s="4"/>
-      <c r="C185" s="4"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
     </row>
     <row r="186" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
@@ -1574,13 +1604,13 @@
     </row>
     <row r="189" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
-      <c r="B189" s="3"/>
-      <c r="C189" s="3"/>
+      <c r="B189" s="4"/>
+      <c r="C189" s="4"/>
     </row>
     <row r="190" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
-      <c r="B190" s="3"/>
-      <c r="C190" s="3"/>
+      <c r="B190" s="4"/>
+      <c r="C190" s="4"/>
     </row>
     <row r="191" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
@@ -2269,7 +2299,7 @@
     </row>
     <row r="328" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
-      <c r="B328" s="1"/>
+      <c r="B328" s="3"/>
       <c r="C328" s="3"/>
     </row>
     <row r="329" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2279,7 +2309,7 @@
     </row>
     <row r="330" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
-      <c r="B330" s="3"/>
+      <c r="B330" s="1"/>
       <c r="C330" s="3"/>
     </row>
     <row r="331" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2444,22 +2474,22 @@
     </row>
     <row r="363" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A363" s="1"/>
-      <c r="B363" s="1"/>
+      <c r="B363" s="3"/>
       <c r="C363" s="3"/>
     </row>
     <row r="364" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A364" s="1"/>
-      <c r="B364" s="1"/>
+      <c r="B364" s="3"/>
       <c r="C364" s="3"/>
     </row>
     <row r="365" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A365" s="1"/>
-      <c r="B365" s="3"/>
+      <c r="B365" s="1"/>
       <c r="C365" s="3"/>
     </row>
     <row r="366" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A366" s="1"/>
-      <c r="B366" s="3"/>
+      <c r="B366" s="1"/>
       <c r="C366" s="3"/>
     </row>
     <row r="367" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2819,8 +2849,8 @@
     </row>
     <row r="438" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A438" s="1"/>
-      <c r="B438" s="1"/>
-      <c r="C438" s="1"/>
+      <c r="B438" s="3"/>
+      <c r="C438" s="3"/>
     </row>
     <row r="439" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A439" s="1"/>
@@ -2829,8 +2859,8 @@
     </row>
     <row r="440" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A440" s="1"/>
-      <c r="B440" s="3"/>
-      <c r="C440" s="3"/>
+      <c r="B440" s="1"/>
+      <c r="C440" s="1"/>
     </row>
     <row r="441" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A441" s="1"/>
@@ -2884,13 +2914,13 @@
     </row>
     <row r="451" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A451" s="1"/>
-      <c r="B451" s="1"/>
-      <c r="C451" s="1"/>
+      <c r="B451" s="3"/>
+      <c r="C451" s="3"/>
     </row>
     <row r="452" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A452" s="1"/>
-      <c r="B452" s="1"/>
-      <c r="C452" s="1"/>
+      <c r="B452" s="3"/>
+      <c r="C452" s="3"/>
     </row>
     <row r="453" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A453" s="1"/>
@@ -2909,13 +2939,13 @@
     </row>
     <row r="456" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A456" s="1"/>
-      <c r="B456" s="3"/>
-      <c r="C456" s="3"/>
+      <c r="B456" s="1"/>
+      <c r="C456" s="1"/>
     </row>
     <row r="457" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A457" s="1"/>
-      <c r="B457" s="3"/>
-      <c r="C457" s="3"/>
+      <c r="B457" s="1"/>
+      <c r="C457" s="1"/>
     </row>
     <row r="458" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A458" s="1"/>
@@ -2984,17 +3014,27 @@
     </row>
     <row r="471" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A471" s="1"/>
-      <c r="B471" s="1"/>
-      <c r="C471" s="1"/>
+      <c r="B471" s="3"/>
+      <c r="C471" s="3"/>
     </row>
     <row r="472" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A472" s="1"/>
-      <c r="B472" s="1"/>
-      <c r="C472" s="1"/>
+      <c r="B472" s="3"/>
+      <c r="C472" s="3"/>
+    </row>
+    <row r="473" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A473" s="1"/>
+      <c r="B473" s="1"/>
+      <c r="C473" s="1"/>
+    </row>
+    <row r="474" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A474" s="1"/>
+      <c r="B474" s="1"/>
+      <c r="C474" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A279:C283">
-    <sortCondition ref="A279:A283"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A281:C285">
+    <sortCondition ref="A281:A285"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tools/languages.xlsx
+++ b/Tools/languages.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/projects/hieunm/chess/Tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46057BD-896D-9347-B9EC-C00727019DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F7D354-4B24-3243-AF79-DFB6D259C079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15840" xr2:uid="{E6764379-1D78-984F-8202-F6CD8653F853}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>Key</t>
   </si>
@@ -159,6 +159,30 @@
   </si>
   <si>
     <t>menu.analytics</t>
+  </si>
+  <si>
+    <t>popup.confirm.ok</t>
+  </si>
+  <si>
+    <t>popup.confirm.cancel</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>Huỷ</t>
+  </si>
+  <si>
+    <t>game.king.captured</t>
+  </si>
+  <si>
+    <t>King has been captured. Game over</t>
+  </si>
+  <si>
+    <t>Vua đã bị bắt. Game kết thúc</t>
   </si>
 </sst>
 </file>
@@ -564,7 +588,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A972E6DD-A464-F34F-8D77-960075701A8D}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C474"/>
+  <dimension ref="A1:C475"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.5" style="2" bestFit="1" customWidth="1"/>
@@ -731,31 +755,49 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+    <row r="16" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="17" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
+    <row r="19" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
@@ -1183,7 +1225,7 @@
       <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A105" s="3"/>
+      <c r="A105" s="1"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
     </row>
@@ -1193,7 +1235,7 @@
       <c r="C106" s="3"/>
     </row>
     <row r="107" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A107" s="1"/>
+      <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
     </row>
@@ -1524,8 +1566,8 @@
     </row>
     <row r="173" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
-      <c r="B173" s="4"/>
-      <c r="C173" s="4"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
     </row>
     <row r="174" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
@@ -1549,8 +1591,8 @@
     </row>
     <row r="178" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
-      <c r="B178" s="3"/>
-      <c r="C178" s="3"/>
+      <c r="B178" s="4"/>
+      <c r="C178" s="4"/>
     </row>
     <row r="179" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
@@ -1589,8 +1631,8 @@
     </row>
     <row r="186" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
-      <c r="B186" s="4"/>
-      <c r="C186" s="4"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
     </row>
     <row r="187" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
@@ -1614,8 +1656,8 @@
     </row>
     <row r="191" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
-      <c r="B191" s="3"/>
-      <c r="C191" s="3"/>
+      <c r="B191" s="4"/>
+      <c r="C191" s="4"/>
     </row>
     <row r="192" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
@@ -2309,12 +2351,12 @@
     </row>
     <row r="330" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
-      <c r="B330" s="1"/>
+      <c r="B330" s="3"/>
       <c r="C330" s="3"/>
     </row>
     <row r="331" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
-      <c r="B331" s="3"/>
+      <c r="B331" s="1"/>
       <c r="C331" s="3"/>
     </row>
     <row r="332" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2484,7 +2526,7 @@
     </row>
     <row r="365" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A365" s="1"/>
-      <c r="B365" s="1"/>
+      <c r="B365" s="3"/>
       <c r="C365" s="3"/>
     </row>
     <row r="366" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2494,7 +2536,7 @@
     </row>
     <row r="367" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A367" s="1"/>
-      <c r="B367" s="3"/>
+      <c r="B367" s="1"/>
       <c r="C367" s="3"/>
     </row>
     <row r="368" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2859,13 +2901,13 @@
     </row>
     <row r="440" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A440" s="1"/>
-      <c r="B440" s="1"/>
-      <c r="C440" s="1"/>
+      <c r="B440" s="3"/>
+      <c r="C440" s="3"/>
     </row>
     <row r="441" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A441" s="1"/>
-      <c r="B441" s="3"/>
-      <c r="C441" s="3"/>
+      <c r="B441" s="1"/>
+      <c r="C441" s="1"/>
     </row>
     <row r="442" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A442" s="1"/>
@@ -2924,8 +2966,8 @@
     </row>
     <row r="453" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A453" s="1"/>
-      <c r="B453" s="1"/>
-      <c r="C453" s="1"/>
+      <c r="B453" s="3"/>
+      <c r="C453" s="3"/>
     </row>
     <row r="454" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A454" s="1"/>
@@ -2949,8 +2991,8 @@
     </row>
     <row r="458" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A458" s="1"/>
-      <c r="B458" s="3"/>
-      <c r="C458" s="3"/>
+      <c r="B458" s="1"/>
+      <c r="C458" s="1"/>
     </row>
     <row r="459" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A459" s="1"/>
@@ -3024,17 +3066,22 @@
     </row>
     <row r="473" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A473" s="1"/>
-      <c r="B473" s="1"/>
-      <c r="C473" s="1"/>
+      <c r="B473" s="3"/>
+      <c r="C473" s="3"/>
     </row>
     <row r="474" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
     </row>
+    <row r="475" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A475" s="1"/>
+      <c r="B475" s="1"/>
+      <c r="C475" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A281:C285">
-    <sortCondition ref="A281:A285"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A282:C286">
+    <sortCondition ref="A282:A286"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tools/languages.xlsx
+++ b/Tools/languages.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/projects/hieunm/chess/Tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518B613D-4ABD-0E4B-8A90-3565CEFBA5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F7D354-4B24-3243-AF79-DFB6D259C079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15840" xr2:uid="{E6764379-1D78-984F-8202-F6CD8653F853}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>Key</t>
   </si>
@@ -47,15 +47,6 @@
     <t>Vietnamese</t>
   </si>
   <si>
-    <t>This field is required</t>
-  </si>
-  <si>
-    <t>Trường này bắt buộc nhập</t>
-  </si>
-  <si>
-    <t>constant.field-required</t>
-  </si>
-  <si>
     <t>settings.header</t>
   </si>
   <si>
@@ -98,9 +89,6 @@
     <t>menu.home</t>
   </si>
   <si>
-    <t>menu.about</t>
-  </si>
-  <si>
     <t>Home</t>
   </si>
   <si>
@@ -113,9 +101,6 @@
     <t>Thông tin</t>
   </si>
   <si>
-    <t>menu.history</t>
-  </si>
-  <si>
     <t>History</t>
   </si>
   <si>
@@ -138,6 +123,66 @@
   </si>
   <si>
     <t>Lượt đánh</t>
+  </si>
+  <si>
+    <t>menu.logout</t>
+  </si>
+  <si>
+    <t>Logout</t>
+  </si>
+  <si>
+    <t>Đăng xuất</t>
+  </si>
+  <si>
+    <t>Chess game</t>
+  </si>
+  <si>
+    <t>Cờ vua</t>
+  </si>
+  <si>
+    <t>menu.app-name</t>
+  </si>
+  <si>
+    <t>menu.users</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>Người dùng</t>
+  </si>
+  <si>
+    <t>Analytic</t>
+  </si>
+  <si>
+    <t>Phân tích</t>
+  </si>
+  <si>
+    <t>menu.analytics</t>
+  </si>
+  <si>
+    <t>popup.confirm.ok</t>
+  </si>
+  <si>
+    <t>popup.confirm.cancel</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>Huỷ</t>
+  </si>
+  <si>
+    <t>game.king.captured</t>
+  </si>
+  <si>
+    <t>King has been captured. Game over</t>
+  </si>
+  <si>
+    <t>Vua đã bị bắt. Game kết thúc</t>
   </si>
 </sst>
 </file>
@@ -543,7 +588,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A972E6DD-A464-F34F-8D77-960075701A8D}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C473"/>
+  <dimension ref="A1:C475"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.5" style="2" bestFit="1" customWidth="1"/>
@@ -564,171 +609,195 @@
     </row>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>10</v>
-      </c>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
@@ -1151,22 +1220,22 @@
       <c r="C103" s="3"/>
     </row>
     <row r="104" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A104" s="3"/>
+      <c r="A104" s="1"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A105" s="3"/>
+      <c r="A105" s="1"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
     </row>
     <row r="106" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A106" s="1"/>
+      <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
     </row>
     <row r="107" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A107" s="1"/>
+      <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
     </row>
@@ -1492,13 +1561,13 @@
     </row>
     <row r="172" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
-      <c r="B172" s="4"/>
-      <c r="C172" s="4"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
     </row>
     <row r="173" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
-      <c r="B173" s="4"/>
-      <c r="C173" s="4"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
     </row>
     <row r="174" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
@@ -1517,13 +1586,13 @@
     </row>
     <row r="177" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
-      <c r="B177" s="3"/>
-      <c r="C177" s="3"/>
+      <c r="B177" s="4"/>
+      <c r="C177" s="4"/>
     </row>
     <row r="178" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
-      <c r="B178" s="3"/>
-      <c r="C178" s="3"/>
+      <c r="B178" s="4"/>
+      <c r="C178" s="4"/>
     </row>
     <row r="179" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
@@ -1557,13 +1626,13 @@
     </row>
     <row r="185" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
-      <c r="B185" s="4"/>
-      <c r="C185" s="4"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
     </row>
     <row r="186" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
-      <c r="B186" s="4"/>
-      <c r="C186" s="4"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
     </row>
     <row r="187" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
@@ -1582,13 +1651,13 @@
     </row>
     <row r="190" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
-      <c r="B190" s="3"/>
-      <c r="C190" s="3"/>
+      <c r="B190" s="4"/>
+      <c r="C190" s="4"/>
     </row>
     <row r="191" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
-      <c r="B191" s="3"/>
-      <c r="C191" s="3"/>
+      <c r="B191" s="4"/>
+      <c r="C191" s="4"/>
     </row>
     <row r="192" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
@@ -2277,7 +2346,7 @@
     </row>
     <row r="329" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
-      <c r="B329" s="1"/>
+      <c r="B329" s="3"/>
       <c r="C329" s="3"/>
     </row>
     <row r="330" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2287,7 +2356,7 @@
     </row>
     <row r="331" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
-      <c r="B331" s="3"/>
+      <c r="B331" s="1"/>
       <c r="C331" s="3"/>
     </row>
     <row r="332" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2452,22 +2521,22 @@
     </row>
     <row r="364" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A364" s="1"/>
-      <c r="B364" s="1"/>
+      <c r="B364" s="3"/>
       <c r="C364" s="3"/>
     </row>
     <row r="365" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A365" s="1"/>
-      <c r="B365" s="1"/>
+      <c r="B365" s="3"/>
       <c r="C365" s="3"/>
     </row>
     <row r="366" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A366" s="1"/>
-      <c r="B366" s="3"/>
+      <c r="B366" s="1"/>
       <c r="C366" s="3"/>
     </row>
     <row r="367" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A367" s="1"/>
-      <c r="B367" s="3"/>
+      <c r="B367" s="1"/>
       <c r="C367" s="3"/>
     </row>
     <row r="368" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2827,8 +2896,8 @@
     </row>
     <row r="439" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A439" s="1"/>
-      <c r="B439" s="1"/>
-      <c r="C439" s="1"/>
+      <c r="B439" s="3"/>
+      <c r="C439" s="3"/>
     </row>
     <row r="440" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A440" s="1"/>
@@ -2837,8 +2906,8 @@
     </row>
     <row r="441" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A441" s="1"/>
-      <c r="B441" s="3"/>
-      <c r="C441" s="3"/>
+      <c r="B441" s="1"/>
+      <c r="C441" s="1"/>
     </row>
     <row r="442" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A442" s="1"/>
@@ -2892,13 +2961,13 @@
     </row>
     <row r="452" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A452" s="1"/>
-      <c r="B452" s="1"/>
-      <c r="C452" s="1"/>
+      <c r="B452" s="3"/>
+      <c r="C452" s="3"/>
     </row>
     <row r="453" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A453" s="1"/>
-      <c r="B453" s="1"/>
-      <c r="C453" s="1"/>
+      <c r="B453" s="3"/>
+      <c r="C453" s="3"/>
     </row>
     <row r="454" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A454" s="1"/>
@@ -2917,13 +2986,13 @@
     </row>
     <row r="457" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A457" s="1"/>
-      <c r="B457" s="3"/>
-      <c r="C457" s="3"/>
+      <c r="B457" s="1"/>
+      <c r="C457" s="1"/>
     </row>
     <row r="458" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A458" s="1"/>
-      <c r="B458" s="3"/>
-      <c r="C458" s="3"/>
+      <c r="B458" s="1"/>
+      <c r="C458" s="1"/>
     </row>
     <row r="459" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A459" s="1"/>
@@ -2992,17 +3061,27 @@
     </row>
     <row r="472" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A472" s="1"/>
-      <c r="B472" s="1"/>
-      <c r="C472" s="1"/>
+      <c r="B472" s="3"/>
+      <c r="C472" s="3"/>
     </row>
     <row r="473" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A473" s="1"/>
-      <c r="B473" s="1"/>
-      <c r="C473" s="1"/>
+      <c r="B473" s="3"/>
+      <c r="C473" s="3"/>
+    </row>
+    <row r="474" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A474" s="1"/>
+      <c r="B474" s="1"/>
+      <c r="C474" s="1"/>
+    </row>
+    <row r="475" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A475" s="1"/>
+      <c r="B475" s="1"/>
+      <c r="C475" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A280:C284">
-    <sortCondition ref="A280:A284"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A282:C286">
+    <sortCondition ref="A282:A286"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tools/languages.xlsx
+++ b/Tools/languages.xlsx
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C471"/>
+  <dimension ref="A1:C465"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -778,2579 +778,2579 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>page.replay.reason-perpetual-check</t>
+          <t>page.replay.reason-surrender</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>{{name}} won by opponent's perpetual check</t>
+          <t>{{name}} surrendered</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>{{name}} thắng do đối thủ chiếu tướng liên tục</t>
+          <t>{{name}} đã đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>page.replay.reason-surrender</t>
+          <t>page.replay.reason-leave</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>{{name}} surrendered</t>
+          <t>{{name}} left the game</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>{{name}} đã đầu hàng</t>
+          <t>{{name}} đã rời trận</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>page.replay.reason-leave</t>
+          <t>page.replay.reason-draw</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>{{name}} left the game</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>{{name}} đã rời trận</t>
+          <t>Hoà</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>page.replay.reason-draw</t>
+          <t>page.replay.reason-timeout</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>{{name}} ran out of total game time</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Hoà</t>
+          <t>{{name}} đã hết giờ cả ván</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>page.replay.reason-timeout</t>
+          <t>page.replay.reason-per-move-timeout</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>{{name}} ran out of total game time</t>
+          <t>{{name}} ran out of time for a move</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>{{name}} đã hết giờ cả ván</t>
+          <t>{{name}} đã hết giờ cho một nước đi</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>page.replay.reason-per-move-timeout</t>
+          <t>page.replay.reason-ended</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>{{name}} ran out of time for a move</t>
+          <t>The game has ended</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>{{name}} đã hết giờ cho một nước đi</t>
+          <t>Ván đấu đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>page.replay.reason-ended</t>
+          <t>menu.app-name</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>The game has ended</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Ván đấu đã kết thúc</t>
+          <t>Cờ vua</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>menu.app-name</t>
+          <t>menu.profile</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Chess</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Cờ vua</t>
+          <t>Trang cá nhân</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>menu.profile</t>
+          <t>menu.messages</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Trang cá nhân</t>
+          <t>Tin nhắn</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>menu.messages</t>
+          <t>menu.change-password</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Tin nhắn</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>menu.change-password</t>
+          <t>menu.guide</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Luật chơi</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>menu.guide</t>
+          <t>menu.announce</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Announcement</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Luật chơi</t>
+          <t>Thông báo</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>menu.announce</t>
+          <t>menu.extra</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>menu.extra</t>
+          <t>menu.leaderboard</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Kiếm tiền</t>
+          <t>Bảng xếp hạng</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>menu.leaderboard</t>
+          <t>menu.setting.button</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Bảng xếp hạng</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>menu.setting.button</t>
+          <t>menu.app-name</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>Cờ vua</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>menu.app-name</t>
+          <t>menu.home</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Chess</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Cờ vua</t>
+          <t>Trang chủ</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>menu.home</t>
+          <t>menu.expired</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Set expired</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Trang chủ</t>
+          <t>Hết hạn token</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>menu.expired</t>
+          <t>menu.logout</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Set expired</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Hết hạn token</t>
+          <t>Đăng xuất</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>menu.logout</t>
+          <t>announce.title</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>Announcement</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất</t>
+          <t>Thông báo</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>announce.title</t>
+          <t>announce.placeholder</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Type an announcement...</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Thông báo</t>
+          <t>Nhập thông báo...</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>announce.placeholder</t>
+          <t>announce.empty</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Type an announcement...</t>
+          <t>No announcements yet</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nhập thông báo...</t>
+          <t>Chưa có thông báo nào</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>announce.empty</t>
+          <t>announce.loading-older</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>No announcements yet</t>
+          <t>Loading older announcements...</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Chưa có thông báo nào</t>
+          <t>Đang tải thông báo cũ hơn...</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>announce.loading-older</t>
+          <t>achievement.title-01</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Loading older announcements...</t>
+          <t>Checkmate an opponent who still has 13 or more pieces</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Đang tải thông báo cũ hơn...</t>
+          <t>Chiếu bí khi đối thủ vẫn còn &gt;= 13 quân</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-01</t>
+          <t>achievement.title-02</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent who still has 13 or more pieces</t>
+          <t>Win your first game</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ vẫn còn &gt;= 13 quân</t>
+          <t>Thắng trận đầu khi chơi game</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-02</t>
+          <t>achievement.title-03</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Win your first game</t>
+          <t>Leave your opponent with no legal moves</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Thắng trận đầu khi chơi game</t>
+          <t>Đánh cho đối thủ không còn nước đi</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-03</t>
+          <t>achievement.title-04</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Leave your opponent with no legal moves</t>
+          <t>Defeat opponents of equal or higher rank in 10 games</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Đánh cho đối thủ không còn nước đi</t>
+          <t>Thắng đối thủ cùng hoặc hơn đẳng cấp 10 ván</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-04</t>
+          <t>achievement.title-05</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Defeat opponents of equal or higher rank in 10 games</t>
+          <t>Hold a draw with only your king remaining</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Thắng đối thủ cùng hoặc hơn đẳng cấp 10 ván</t>
+          <t>Cầm hoà đối thủ khi chỉ còn tướng</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-05</t>
+          <t>achievement.title-06</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Hold a draw with only your king remaining</t>
+          <t>Win 100 games</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Cầm hoà đối thủ khi chỉ còn tướng</t>
+          <t>Thắng 100 trận</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-06</t>
+          <t>achievement.title-07</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Win 100 games</t>
+          <t>Draw 50 games</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Thắng 100 trận</t>
+          <t>Hoà 50 trận</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-07</t>
+          <t>achievement.title-08</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Draw 50 games</t>
+          <t>Checkmate an opponent with only 1 attacking piece remaining</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Hoà 50 trận</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn 1 quân tấn công</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-08</t>
+          <t>achievement.title-09</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only 1 attacking piece remaining</t>
+          <t>Checkmate an opponent with only a knight remaining</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn 1 quân tấn công</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn mã</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-09</t>
+          <t>achievement.title-10</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a knight remaining</t>
+          <t>Checkmate an opponent with only a pawn remaining</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn mã</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn tốt</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-10</t>
+          <t>achievement.title-11</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a pawn remaining</t>
+          <t>Checkmate an opponent with only a cannon remaining</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn tốt</t>
+          <t>Chiếu bí khi đối thủ khi chỉ còn pháo</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-11</t>
+          <t>achievement.title-12</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Checkmate an opponent with only a cannon remaining</t>
+          <t>Defeat opponents with master rank in 50 games</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Chiếu bí khi đối thủ khi chỉ còn pháo</t>
+          <t>Thắng đối thủ có đẳng cấp kỳ thủ 50 ván</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>achievement.title-12</t>
+          <t>achievement.tab-title</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Defeat opponents with master rank in 50 games</t>
+          <t>Achievements</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Thắng đối thủ có đẳng cấp kỳ thủ 50 ván</t>
+          <t>Thành tựu</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>achievement.tab-title</t>
+          <t>achievement.messages.success</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Achievements</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Thành tựu</t>
+          <t>Thành công</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>achievement.messages.success</t>
+          <t>achievement.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Thành công</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>achievement.messages.invalid-user-id</t>
+          <t>achievement.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Lỗi máy chủ</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>achievement.messages.internal-server-error</t>
+          <t>chat.conversation.you</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ</t>
+          <t>Bạn</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>chat.conversation.you</t>
+          <t>chat.messages.unread</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Unread messages</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Bạn</t>
+          <t>Tin nhắn chưa đọc</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>chat.messages.unread</t>
+          <t>search.user.title</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Unread messages</t>
+          <t>Search user</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Tin nhắn chưa đọc</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>search.user.title</t>
+          <t>search.user.placeholder</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Search user</t>
+          <t>Search user...</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm</t>
+          <t>Tìm kiếm người dùng...</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>search.user.placeholder</t>
+          <t>search.user.no-results</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Search user...</t>
+          <t>No users found</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm người dùng...</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>search.user.no-results</t>
+          <t>search.button.search</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>No users found</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>search.button.search</t>
+          <t>leaderboard.title</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Tìm kiếm</t>
+          <t>Bảng xếp hạng</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>leaderboard.title</t>
+          <t>leaderboard.search-placeholder</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Search user...</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Bảng xếp hạng</t>
+          <t>Tìm kiếm người dùng...</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>leaderboard.search-placeholder</t>
+          <t>leaderboard.no-results</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Search user...</t>
+          <t>No users found</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Tìm kiếm người dùng...</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>leaderboard.no-results</t>
+          <t>leaderboard.empty</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>No users found</t>
+          <t>No players yet</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Chưa có người chơi nào</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>leaderboard.empty</t>
+          <t>dashboard.page.title</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>No players yet</t>
+          <t>Room list</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Chưa có người chơi nào</t>
+          <t>Danh sách phòng</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>dashboard.page.title</t>
+          <t>dashboard.filters.all</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Room list</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Danh sách phòng</t>
+          <t>Tất cả</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.all</t>
+          <t>dashboard.filters.available</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Tất cả</t>
+          <t>Chờ</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.available</t>
+          <t>dashboard.filters.playing</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Playing</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Chờ</t>
+          <t>Đang chơi</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>dashboard.filters.playing</t>
+          <t>dashboard.feedback.empty</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Playing</t>
+          <t>No room tables match the selected filter.</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Đang chơi</t>
+          <t>Không có bàn chơi phù hợp với bộ lọc đã chọn.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.empty</t>
+          <t>dashboard.feedback.error</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>No room tables match the selected filter.</t>
+          <t>Unable to load room tables.</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Không có bàn chơi phù hợp với bộ lọc đã chọn.</t>
+          <t>Không tải được danh sách phòng chơi.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>dashboard.feedback.error</t>
+          <t>dashboard.status.unknown</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Unable to load room tables.</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Không tải được danh sách phòng chơi.</t>
+          <t>Không xác định</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>dashboard.status.unknown</t>
+          <t>dashboard.room.create</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Create room</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Không xác định</t>
+          <t>Tạo phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>dashboard.room.create</t>
+          <t>dashboard.popup.piece-selection</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Create room</t>
+          <t>Select team</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Tạo phòng chơi</t>
+          <t>Chọn quân</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.piece-selection</t>
+          <t>dashboard.popup.red-first</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Select team</t>
+          <t>Red first</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Chọn quân</t>
+          <t>Đỏ tiên</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.red-first</t>
+          <t>dashboard.popup.pve-mode</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Red first</t>
+          <t>PVE mode</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Đỏ tiên</t>
+          <t>Chơi với máy</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.pve-mode</t>
+          <t>dashboard.popup.bet-amount</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>PVE mode</t>
+          <t>Bet amount</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Chơi với máy</t>
+          <t>Giá trị cược</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.bet-amount</t>
+          <t>dashboard.popup.time-limit</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Bet amount</t>
+          <t>Time limit</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Giá trị cược</t>
+          <t>Giới hạn thời gian</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-limit</t>
+          <t>dashboard.popup.time-limit-per-player</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Time limit</t>
+          <t>Time per player</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Giới hạn thời gian</t>
+          <t>Thời gian mỗi người</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-limit-per-player</t>
+          <t>dashboard.popup.time-unlimited</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Time per player</t>
+          <t>Unlimited</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Thời gian mỗi người</t>
+          <t>Không giới hạn</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-unlimited</t>
+          <t>dashboard.popup.time-minutes</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Unlimited</t>
+          <t>{0} min</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Không giới hạn</t>
+          <t>{0} phút</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-minutes</t>
+          <t>dashboard.popup.time-seconds</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>{0} min</t>
+          <t>{0}s</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>{0} phút</t>
+          <t>{0}s</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-seconds</t>
+          <t>dashboard.popup.time-off</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>{0}s</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>{0}s</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-off</t>
+          <t>dashboard.popup.time-increment</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Bonus per move</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Tắt</t>
+          <t>Cộng giờ mỗi nước</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-increment</t>
+          <t>dashboard.popup.time-per-move</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Bonus per move</t>
+          <t>Time per move</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Cộng giờ mỗi nước</t>
+          <t>Thời gian mỗi nước</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.time-per-move</t>
+          <t>dashboard.popup.room-name-label</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Time per move</t>
+          <t>Room table name</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Thời gian mỗi nước</t>
+          <t>Tên phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-label</t>
+          <t>dashboard.popup.room-name-helptext</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Room table name</t>
+          <t>is required</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng chơi</t>
+          <t>không được để trống</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.room-name-helptext</t>
+          <t>dashboard.popup.play</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>is required</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>không được để trống</t>
+          <t>Chơi</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.play</t>
+          <t>dashboard.popup.view</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>View</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Chơi</t>
+          <t>Xem</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>dashboard.popup.view</t>
+          <t>settings.header</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Xem</t>
+          <t>Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>settings.header</t>
+          <t>settings.language</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt</t>
+          <t>Ngôn ngữ</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>settings.language</t>
+          <t>settings.dark-mode</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Dark mode</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Ngôn ngữ</t>
+          <t>Chế độ tối</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>settings.dark-mode</t>
+          <t>settings.sound</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Dark mode</t>
+          <t>Sound</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Chế độ tối</t>
+          <t>Âm thanh</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>settings.sound</t>
+          <t>settings.debug-mode</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Debug mode</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Âm thanh</t>
+          <t>Chế độ test</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>settings.debug-mode</t>
+          <t>settings.connected-accounts.label</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Debug mode</t>
+          <t>Connected accounts</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Chế độ test</t>
+          <t>Tài khoản liên kết</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.label</t>
+          <t>settings.connected-accounts.link-facebook</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Connected accounts</t>
+          <t>Link Facebook</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản liên kết</t>
+          <t>Liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-facebook</t>
+          <t>settings.connected-accounts.unlink-facebook</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Link Facebook</t>
+          <t>Unlink Facebook</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Liên kết Facebook</t>
+          <t>Huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.unlink-facebook</t>
+          <t>settings.connected-accounts.link-success</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Unlink Facebook</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Huỷ liên kết Facebook</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-success</t>
+          <t>settings.connected-accounts.unlink-success</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.unlink-success</t>
+          <t>settings.connected-accounts.link-error</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>Could not update Facebook link</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Không cập nhật được liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>settings.connected-accounts.link-error</t>
+          <t>settings.close</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Could not update Facebook link</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Không cập nhật được liên kết Facebook</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>settings.close</t>
+          <t>popup.alert.title</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Cảnh báo</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>popup.alert.title</t>
+          <t>popup.confirm.title</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Cảnh báo</t>
+          <t>Xác nhận</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.title</t>
+          <t>popup.confirm.ok</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận</t>
+          <t>Ok</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.ok</t>
+          <t>popup.confirm.cancel</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>popup.confirm.cancel</t>
+          <t>game.general.captured</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>General has been captured. Room over</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Tướng đã bị bắt. Game kết thúc</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>game.general.captured</t>
+          <t>game.general.in-check</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>General has been captured. Room over</t>
+          <t>Your general is under attack</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Tướng đã bị bắt. Game kết thúc</t>
+          <t>Tướng của bạn đang bị chiếu</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>game.general.in-check</t>
+          <t>game.label.win</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Your general is under attack</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Tướng của bạn đang bị chiếu</t>
+          <t>Thắng</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>game.perpetual-check.warning-self</t>
+          <t>game.label.draw</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>You are perpetual checking. If you make one more repeated check, you will lose</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang chiếu quẩn, nếu thực hiện 1 nước nữa, bạn sẽ bị xử thua</t>
+          <t>Hoà</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>game.perpetual-check.warning-sent</t>
+          <t>game.label.lose</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>A perpetual-check warning has been sent to your opponent</t>
+          <t>Lose</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Đã gửi cảnh báo chiếu quẩn cho đối thủ</t>
+          <t>Thua</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>game.label.win</t>
+          <t>room.bot-difficulty.title</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Select Bot Difficulty</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Thắng</t>
+          <t>Chọn độ khó của Bot</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>game.label.draw</t>
+          <t>room.bot-difficulty.beginner</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Beginner</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Hoà</t>
+          <t>Mới bắt đầu</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>game.label.lose</t>
+          <t>room.bot-difficulty.amateur</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Lose</t>
+          <t>Amateur</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Thua</t>
+          <t>Nghiệp dư</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.title</t>
+          <t>room.bot-difficulty.intermediate</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Select Bot Difficulty</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Chọn độ khó của Bot</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.beginner</t>
+          <t>room.bot-difficulty.advanced</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Mới bắt đầu</t>
+          <t>Nâng cao</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.amateur</t>
+          <t>room.bot-difficulty.master</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Amateur</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Nghiệp dư</t>
+          <t>Lão luyện</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.intermediate</t>
+          <t>login.page.title</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.advanced</t>
+          <t>login.form.title</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Nâng cao</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.master</t>
+          <t>login.username.label</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Lão luyện</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="130" ht="36" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>login.page.title</t>
+          <t>login.username.placeholder</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>login.form.title</t>
+          <t>login.password.label</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>login.username.label</t>
+          <t>login.password.placeholder</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>login.username.placeholder</t>
+          <t>login.password.show</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>login.password.label</t>
+          <t>login.password.hide</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="135" ht="36" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>login.password.placeholder</t>
+          <t>login.form.error1</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t xml:space="preserve">Login failed. Please check your credentials </t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>login.password.show</t>
+          <t>login.form.forgot-password</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>login.password.hide</t>
+          <t>login.form.register</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>login.form.error1</t>
+          <t>login.form.submit</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login failed. Please check your credentials </t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>login.form.forgot-password</t>
+          <t>login.form.or</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>hoặc</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>login.form.register</t>
+          <t>login.google.load-error</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Could not load Google Sign-In</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Không tải được đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>login.form.submit</t>
+          <t>login.facebook.button</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Sign-in with Facebook</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Đăng nhập với Facebook</t>
         </is>
       </c>
     </row>
     <row r="142" ht="36" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>login.form.or</t>
+          <t>login.messages.incorrect-login</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>Invalid username or password</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>hoặc</t>
+          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>login.google.load-error</t>
+          <t>login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Could not load Google Sign-In</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Không tải được đăng nhập Google</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>login.facebook.button</t>
+          <t>login.messages.missing-credentials</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Sign-in with Facebook</t>
+          <t>Username and password are required</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với Facebook</t>
+          <t>Tên người dùng và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>login.messages.incorrect-login</t>
+          <t>login.messages.success</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Invalid username or password</t>
+          <t>Login successful</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>login.messages.internal-server-error</t>
+          <t>notfound.title</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Page Not Found</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trang không tìm thấy</t>
         </is>
       </c>
     </row>
     <row r="147" ht="36" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>login.messages.missing-credentials</t>
+          <t>notfound.description</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Username and password are required</t>
+          <t>The page you are looking for does not exist or has been moved.</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng và mật khẩu là bắt buộc</t>
+          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
         </is>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>login.messages.success</t>
+          <t>notfound.home</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Login successful</t>
+          <t>Go to Home</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Về trang chủ</t>
         </is>
       </c>
     </row>
     <row r="149" ht="36" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>notfound.title</t>
+          <t>notfound.back</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Page Not Found</t>
+          <t>Go Back</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Trang không tìm thấy</t>
+          <t>Quay lại</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>notfound.description</t>
+          <t>register.confirm-password.error1</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>The page you are looking for does not exist or has been moved.</t>
+          <t>Confirm password does not match password</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
+          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>notfound.home</t>
+          <t>register.confirm-password.label</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Go to Home</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Về trang chủ</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>notfound.back</t>
+          <t>register.confirm-password.placeholder</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Go Back</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Quay lại</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.error1</t>
+          <t>register.display-name.label</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Confirm password does not match password</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.label</t>
+          <t>register.display-name.placeholder</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.placeholder</t>
+          <t>register.email.error1</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.label</t>
+          <t>register.email.label</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.placeholder</t>
+          <t>register.email.placeholder</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>register.email.error1</t>
+          <t>register.form.login</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="159" ht="36" customHeight="1">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>register.email.label</t>
+          <t>register.form.submit</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>register.email.placeholder</t>
+          <t>register.form.success</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Registration successful. Redirecting to login...</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Đăng ký thành công. Đang chuyển hướng...</t>
         </is>
       </c>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>register.form.login</t>
+          <t>register.form.title</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>register.form.submit</t>
+          <t>register.gender.female</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Nữ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>register.form.success</t>
+          <t>register.gender.label</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Registration successful. Redirecting to login...</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký thành công. Đang chuyển hướng...</t>
+          <t>Giới tính</t>
         </is>
       </c>
     </row>
     <row r="164" ht="36" customHeight="1">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>register.form.title</t>
+          <t>register.gender.male</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Nam</t>
         </is>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>register.gender.female</t>
+          <t>register.gender.select</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Select gender</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Chọn giới tính</t>
         </is>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>register.gender.label</t>
+          <t>register.page.title</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Giới tính</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>register.gender.male</t>
+          <t>register.password.error1</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>register.gender.select</t>
+          <t>register.password.hide</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Select gender</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Chọn giới tính</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>register.page.title</t>
+          <t>register.password.label</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>register.password.error1</t>
+          <t>register.password.placeholder</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>register.password.hide</t>
+          <t>register.password.show</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>register.password.label</t>
+          <t>register.username.error1</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
         </is>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>register.password.placeholder</t>
+          <t>register.username.label</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>register.password.show</t>
+          <t>register.username.placeholder</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>register.username.error1</t>
+          <t>forgot-password.page.title</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="176" ht="36" customHeight="1">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>register.username.label</t>
+          <t>forgot-password.form.title</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>register.username.placeholder</t>
+          <t>forgot-password.form.login</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.page.title</t>
+          <t>forgot-password.form.submit</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -3362,2953 +3362,2953 @@
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.title</t>
+          <t>forgot-password.form.success</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Check your email for reset password details.</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.login</t>
+          <t>forgot-password.form.error1</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Forgot password failed.</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Quên mật khẩu không thành công.</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.submit</t>
+          <t>reset-password.page.title</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.success</t>
+          <t>reset-password.form.title</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Check your email for reset password details.</t>
+          <t>Reset your password</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
+          <t>Đặt lại mật khẩu của bạn</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.error1</t>
+          <t>reset-password.form.submit</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Forgot password failed.</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu không thành công.</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>reset-password.page.title</t>
+          <t>reset-password.form.error1</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>An error occurred while resetting your password. Please try again.</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="185" ht="36" customHeight="1">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.title</t>
+          <t>reset-password.form.invalid-token</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Reset your password</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu của bạn</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.submit</t>
+          <t>reset-password.form.success</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Password reset successfully. Redirecting to login...</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
         </is>
       </c>
     </row>
     <row r="187" ht="36" customHeight="1">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.error1</t>
+          <t>reset-password.action.back-to-login</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>An error occurred while resetting your password. Please try again.</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
+          <t>Quay lại trang chủ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.invalid-token</t>
+          <t>auth-middleware.messages.invalid-token-payload</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Invalid token payload</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Payload của token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.success</t>
+          <t>auth-middleware.messages.session-not-found</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Password reset successfully. Redirecting to login...</t>
+          <t>Session not found</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
+          <t>Không tìm thấy phiên</t>
         </is>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>reset-password.action.back-to-login</t>
+          <t>auth-middleware.messages.token-expired</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Token is expired</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Quay lại trang chủ</t>
+          <t>Token đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.invalid-token-payload</t>
+          <t>auth-middleware.messages.token-invalid</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Invalid token payload</t>
+          <t>Token is invalid</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Payload của token không hợp lệ</t>
+          <t>Token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.session-not-found</t>
+          <t>auth-middleware.messages.token-required</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Session not found</t>
+          <t>Token not provided</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phiên</t>
+          <t>Token không được cung cấp</t>
         </is>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-expired</t>
+          <t>auth-middleware.messages.token-subject-mismatch</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Token is expired</t>
+          <t>Token subject mismatch</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Token đã hết hạn</t>
+          <t>Token chủ đề không khớp</t>
         </is>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-invalid</t>
+          <t>auth-middleware.messages.token-validation-failed</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Token is invalid</t>
+          <t>Token validation failed</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Token không hợp lệ</t>
+          <t>Xác thực token không thành công</t>
         </is>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-required</t>
+          <t>create-room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Token not provided</t>
+          <t>You do not have enough balance to create a room with this bet</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Token không được cung cấp</t>
+          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-subject-mismatch</t>
+          <t>create-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Token subject mismatch</t>
+          <t>Internal server error while creating room</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Token chủ đề không khớp</t>
+          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-validation-failed</t>
+          <t>create-room.messages.invalid-bet-amount</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Token validation failed</t>
+          <t>Bet amount is required and must be one of the acceptable values</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Xác thực token không thành công</t>
+          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.insufficient-amount</t>
+          <t>create-room.messages.invalid-time-limit</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to create a room with this bet</t>
+          <t>Invalid time limit</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
+          <t>Thời gian không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.internal-server-error</t>
+          <t>create-room.messages.invalid-time-increment</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while creating room</t>
+          <t>Invalid bonus per move</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
+          <t>Thời gian cộng mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-bet-amount</t>
+          <t>create-room.messages.invalid-time-per-move</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Bet amount is required and must be one of the acceptable values</t>
+          <t>Invalid time per move</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
+          <t>Thời gian mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-time-limit</t>
+          <t>create-room.messages.invalid-redFirst</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Invalid time limit</t>
+          <t>'redFirst' must be a boolean</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Thời gian không hợp lệ</t>
+          <t>'redFirst' phải là giá trị boolean</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-time-increment</t>
+          <t>create-room.messages.invalid-team-name</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Invalid bonus per move</t>
+          <t>Team name must be either 'red', 'black', or null</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Thời gian cộng mỗi nước không hợp lệ</t>
+          <t>Tên đội phải là 'red', 'black' hoặc null</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-time-per-move</t>
+          <t>create-room.messages.name-required</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Invalid time per move</t>
+          <t>Room name (tableName) is required and must not be empty</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Thời gian mỗi nước không hợp lệ</t>
+          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
         </is>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-redFirst</t>
+          <t>create-room.messages.room-created</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' must be a boolean</t>
+          <t>Room created successfully</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' phải là giá trị boolean</t>
+          <t>Phòng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-team-name</t>
+          <t>fetch-rooms.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Team name must be either 'red', 'black', or null</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Tên đội phải là 'red', 'black' hoặc null</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.name-required</t>
+          <t>fetch-rooms.messages.invalid-status</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Room name (tableName) is required and must not be empty</t>
+          <t>Query parameter 'status' must be an integer</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
+          <t>Tham số truy vấn 'status' phải là số nguyên</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.room-created</t>
+          <t>fetch-rooms.messages.success</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Room created successfully</t>
+          <t>Fetch rooms successfully</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Phòng được tạo thành công</t>
+          <t>Lấy phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.internal-server-error</t>
+          <t>forgot-password.messages.email-not-found</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Email does not exist</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Email không tồn tại</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.invalid-status</t>
+          <t>forgot-password.messages.email-service-not-configured</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Query parameter 'status' must be an integer</t>
+          <t>Email service is not configured</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Tham số truy vấn 'status' phải là số nguyên</t>
+          <t>Dịch vụ email chưa được cấu hình</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.success</t>
+          <t>forgot-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Fetch rooms successfully</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Lấy phòng thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="36" customHeight="1">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-not-found</t>
+          <t>forgot-password.messages.invalid-email-format</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Email does not exist</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Email không tồn tại</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-service-not-configured</t>
+          <t>forgot-password.messages.missing-email</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Email service is not configured</t>
+          <t>Email is required</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Dịch vụ email chưa được cấu hình</t>
+          <t>Email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.internal-server-error</t>
+          <t>forgot-password.messages.success</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Forgot password email sent</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Email đặt lại mật khẩu đã được gửi</t>
         </is>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.invalid-email-format</t>
+          <t>join-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.missing-email</t>
+          <t>join-room.messages.invalid-team</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Email is required</t>
+          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Email là bắt buộc</t>
+          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.success</t>
+          <t>join-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Forgot password email sent</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Email đặt lại mật khẩu đã được gửi</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.internal-server-error</t>
+          <t>join-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-team</t>
+          <t>join-room.messages.success</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
+          <t>Successfully joined the room</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
+          <t>Tham gia phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-room-id</t>
+          <t>join-room.messages.team-seat-occupied</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Selected team seat is already occupied</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Vị trí đội đã chọn đã có người chơi</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.room-not-found</t>
+          <t>kick-user.messages.cannot-kick-self</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>You cannot kick yourself</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Bạn không thể kick chính mình</t>
         </is>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.success</t>
+          <t>kick-user.messages.forbidden</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Successfully joined the room</t>
+          <t>Only the host can kick users</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Tham gia phòng thành công</t>
+          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
         </is>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.team-seat-occupied</t>
+          <t>kick-user.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Selected team seat is already occupied</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Vị trí đội đã chọn đã có người chơi</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.cannot-kick-self</t>
+          <t>kick-user.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>You cannot kick yourself</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Bạn không thể kick chính mình</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.forbidden</t>
+          <t>kick-user.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Only the host can kick users</t>
+          <t>Field 'userId' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
+          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.internal-server-error</t>
+          <t>kick-user.messages.room-not-found</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-room-id</t>
+          <t>kick-user.messages.room-not-waiting</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>You can only kick users while the room is waiting</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-user-id</t>
+          <t>kick-user.messages.success</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Field 'userId' is required and must be a positive integer</t>
+          <t>User has been kicked</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
+          <t>Người dùng đã bị kick</t>
         </is>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-found</t>
+          <t>kick-user.messages.user-not-in-room</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>User is not in this room</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Người dùng không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-waiting</t>
+          <t>kick-user.messages.you-were-kicked</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>You can only kick users while the room is waiting</t>
+          <t>You have been removed from the room by the host</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
+          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
         </is>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.success</t>
+          <t>leave-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>User has been kicked</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Người dùng đã bị kick</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.user-not-in-room</t>
+          <t>leave-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>User is not in this room</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Người dùng không trong phòng này</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.you-were-kicked</t>
+          <t>leave-room.messages.player-not-in-room</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>You have been removed from the room by the host</t>
+          <t>Player is not in this room</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
+          <t>Người chơi không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.internal-server-error</t>
+          <t>leave-room.messages.success</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Leave room successfully</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Rời phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.invalid-room-id</t>
+          <t>load-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.player-not-in-room</t>
+          <t>load-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Player is not in this room</t>
+          <t>Room ID must be a positive integer</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Người chơi không trong phòng này</t>
+          <t>ID phòng phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.success</t>
+          <t>load-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Leave room successfully</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Rời phòng thành công</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.internal-server-error</t>
+          <t>load-room.messages.success</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Load room successfully</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tải phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.invalid-room-id</t>
+          <t>google-login.messages.email-not-verified</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Room ID must be a positive integer</t>
+          <t>Your Google email is not verified</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>ID phòng phải là số nguyên dương</t>
+          <t>Email Google của bạn chưa được xác minh</t>
         </is>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.room-not-found</t>
+          <t>google-login.messages.failed</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Login failed</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Đăng nhập không thành công</t>
         </is>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.success</t>
+          <t>google-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Load room successfully</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Tải phòng thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.email-not-verified</t>
+          <t>google-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Your Google email is not verified</t>
+          <t>Invalid Google credential</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Email Google của bạn chưa được xác minh</t>
+          <t>Thông tin đăng nhập Google không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.failed</t>
+          <t>google-login.messages.missing-credential</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Login failed</t>
+          <t>Google credential is required</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công</t>
+          <t>Thiếu thông tin đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.internal-server-error</t>
+          <t>facebook-login.messages.missing-token</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.invalid-token</t>
+          <t>facebook-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Invalid Google credential</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Google không hợp lệ</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.missing-credential</t>
+          <t>facebook-login.messages.not-linked</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Google credential is required</t>
+          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Google</t>
+          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.missing-token</t>
+          <t>facebook-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.invalid-token</t>
+          <t>facebook-link.messages.missing-token</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.not-linked</t>
+          <t>facebook-link.messages.invalid-token</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.internal-server-error</t>
+          <t>facebook-link.messages.linked</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.missing-token</t>
+          <t>facebook-link.messages.already-linked</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>This Facebook account is already linked to your account</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
         </is>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.invalid-token</t>
+          <t>facebook-link.messages.linked-to-other</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>This Facebook account is already linked to another account</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
         </is>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked</t>
+          <t>facebook-link.messages.already-has-facebook</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>You already linked a different Facebook account</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
         </is>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-linked</t>
+          <t>facebook-link.messages.unlinked</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to your account</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked-to-other</t>
+          <t>facebook-link.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to another account</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-has-facebook</t>
+          <t>logout.messages.already-inactive</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>You already linked a different Facebook account</t>
+          <t>Session already inactive</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
+          <t>Phiên đã ngưng hoạt động</t>
         </is>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.unlinked</t>
+          <t>logout.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.internal-server-error</t>
+          <t>logout.messages.success</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Logout successful</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Đăng xuất thành công</t>
         </is>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.already-inactive</t>
+          <t>refresh-token.messages.missing-refresh-token</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Session already inactive</t>
+          <t>Missing refresh token cookie</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Phiên đã ngưng hoạt động</t>
+          <t>Thiếu cookie token làm mới</t>
         </is>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.internal-server-error</t>
+          <t>refresh-token.messages.mismatch-or-expired</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Refresh token mismatch or expired</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thiếu refresh token hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="260" ht="36" customHeight="1">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.success</t>
+          <t>refresh-token.messages.success</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Logout successful</t>
+          <t>Token refreshed</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất thành công</t>
+          <t>Token đã làm mới</t>
         </is>
       </c>
     </row>
     <row r="261" ht="36" customHeight="1">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.missing-refresh-token</t>
+          <t>register.messages.email-exists</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Missing refresh token cookie</t>
+          <t>Email already exists</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Thiếu cookie token làm mới</t>
+          <t>Email đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.mismatch-or-expired</t>
+          <t>register.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Refresh token mismatch or expired</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Thiếu refresh token hoặc đã hết hạn</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.success</t>
+          <t>register.messages.missing-fields</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Token refreshed</t>
+          <t>Username, password, gender, displayName and email are required</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Token đã làm mới</t>
+          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>register.messages.email-exists</t>
+          <t>register.messages.success</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Email already exists</t>
+          <t>User created successfully</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Email đã tồn tại</t>
+          <t>Người dùng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="265" ht="17" customHeight="1">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>register.messages.internal-server-error</t>
+          <t>register.messages.username-exists</t>
         </is>
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Username already exists</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tên người dùng đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>register.messages.missing-fields</t>
+          <t>reset-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Username, password, gender, displayName and email are required</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>register.messages.success</t>
+          <t>reset-password.messages.invalid-or-expired-token</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>User created successfully</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Người dùng được tạo thành công</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>register.messages.username-exists</t>
+          <t>reset-password.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Username already exists</t>
+          <t>Invalid user id</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng đã tồn tại</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.internal-server-error</t>
+          <t>reset-password.messages.missing-id-or-token</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>ID and token are required</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>ID và token là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-or-expired-token</t>
+          <t>reset-password.messages.missing-userId-or-password</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>UserId and password are required</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>UserId và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="271" ht="36" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-user-id</t>
+          <t>reset-password.messages.token-valid</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Invalid user id</t>
+          <t>Reset password token is valid</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Token đặt lại mật khẩu hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="36" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-id-or-token</t>
+          <t>reset-password.messages.user-not-found</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>ID and token are required</t>
+          <t>User not found</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>ID và token là bắt buộc</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-userId-or-password</t>
+          <t>room.actions.start-room</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>UserId and password are required</t>
+          <t>Start room</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>UserId và mật khẩu là bắt buộc</t>
+          <t>Bắt đầu chơi</t>
         </is>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.token-valid</t>
+          <t>room.actions.challenge</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Reset password token is valid</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu hợp lệ</t>
+          <t>Vào chơi</t>
         </is>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>reset-password.messages.user-not-found</t>
+          <t>room.actions.leave-seat</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>Leave seat</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Ra xem</t>
         </is>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>room.actions.start-room</t>
+          <t>room.actions.undo</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Start room</t>
+          <t>Undo</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu chơi</t>
+          <t>Hoán tác</t>
         </is>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>room.actions.challenge</t>
+          <t>room.actions.surrender</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Surrender</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Vào chơi</t>
+          <t>Đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>room.actions.leave-seat</t>
+          <t>room.actions.draw</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Leave seat</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Ra xem</t>
+          <t>Hòa</t>
         </is>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>room.actions.undo</t>
+          <t>room.actions.back-home</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Undo</t>
+          <t>Back to home</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Hoán tác</t>
+          <t>Thoát phòng</t>
         </is>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>room.actions.surrender</t>
+          <t>room.actions.flip-board</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Surrender</t>
+          <t>Flip board</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Đầu hàng</t>
+          <t>Đảo chiều bàn cờ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>room.actions.draw</t>
+          <t>room.actions.accept-draw</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Hòa</t>
+          <t>Chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-home</t>
+          <t>room.actions.reject-draw</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Back to home</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Thoát phòng</t>
+          <t>Từ chối</t>
         </is>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>room.actions.flip-board</t>
+          <t>room.actions.send-pm</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Flip board</t>
+          <t>Send PM</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Đảo chiều bàn cờ</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>room.actions.accept-draw</t>
+          <t>room.actions.view-history</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>History</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Chấp nhận</t>
+          <t>Lịch sử</t>
         </is>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>room.actions.reject-draw</t>
+          <t>room.actions.kick</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Từ chối</t>
+          <t>Kick</t>
         </is>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>room.actions.send-pm</t>
+          <t>room.actions.back-to-room</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Send PM</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Quay lại phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>room.actions.view-history</t>
+          <t>room.actions.chat</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Room chat</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử</t>
+          <t>Phòng chat</t>
         </is>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>room.actions.kick</t>
+          <t>room.messages.draw-accepted</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Opponent accepted the draw</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Đối phương đã đồng ý hòa</t>
         </is>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-to-room</t>
+          <t>room.messages.draw-rejected</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Back to room</t>
+          <t>Opponent rejected the draw</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Quay lại phòng chơi</t>
+          <t>Đối phương từ chối hòa</t>
         </is>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>room.actions.chat</t>
+          <t>room.messages.opponent-surrendered</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Room chat</t>
+          <t>Opponent surrendered! You won!</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Phòng chat</t>
+          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
         </is>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-accepted</t>
+          <t>room.messages.confirm-leave</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Opponent accepted the draw</t>
+          <t>Are you sure you want to leave room?</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đồng ý hòa</t>
+          <t>Bạn có chắc muốn rời bàn chơi?</t>
         </is>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-rejected</t>
+          <t>room.messages.confirm-surrender</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Opponent rejected the draw</t>
+          <t>Are you sure you want to surrender?</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Đối phương từ chối hòa</t>
+          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
         </is>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>room.messages.opponent-surrendered</t>
+          <t>room.messages.confirm-draw</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Opponent surrendered! You won!</t>
+          <t>Are you sure you want to draw?</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
+          <t>Bạn có chắc chắn muốn hòa không?</t>
         </is>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-leave</t>
+          <t>room.messages.confirm-accept-draw</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to leave room?</t>
+          <t>Opponent has proposed a draw. Do you accept?</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc muốn rời bàn chơi?</t>
+          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
         </is>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-surrender</t>
+          <t>room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to surrender?</t>
+          <t>You do not have enough balance to join this room</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
+          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
         </is>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-draw</t>
+          <t>room.messages.will-leave-current-room</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to draw?</t>
+          <t>You are currently in another room. Joining this room will remove you from the current room</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn hòa không?</t>
+          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
         </is>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-accept-draw</t>
+          <t>room.messages.game-ended</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Opponent has proposed a draw. Do you accept?</t>
+          <t>Game ended</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
+          <t>Ván đấu đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>room.messages.insufficient-amount</t>
+          <t>room.messages.you-win</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to join this room</t>
+          <t>You win</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
+          <t>Bạn đã chiến thắng</t>
         </is>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>room.messages.will-leave-current-room</t>
+          <t>room.messages.you-lose</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>You are currently in another room. Joining this room will remove you from the current room</t>
+          <t>You lose</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
+          <t>Bạn đã thua</t>
         </is>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>room.messages.game-ended</t>
+          <t>room.messages.you-draw</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Game ended</t>
+          <t>The game is a draw</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Ván đấu đã kết thúc</t>
+          <t>Ván đấu hòa</t>
         </is>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-win</t>
+          <t>room.messages.you-win-per-move-timeout</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>You win</t>
+          <t>You win — your opponent ran out of move time</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã chiến thắng</t>
+          <t>Bạn thắng vì đối thủ hết giờ đi một nước</t>
         </is>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-lose</t>
+          <t>room.messages.you-lose-per-move-timeout</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>You lose</t>
+          <t>You lose — you ran out of move time</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã thua</t>
+          <t>Bạn thua do hết giờ đi một nước</t>
         </is>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-draw</t>
+          <t>room.messages.spectator-win-checkmate</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>The game is a draw</t>
+          <t>{0} won by checkmate</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Ván đấu hòa</t>
+          <t>{0} thắng do chiếu bí</t>
         </is>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-win-perpetual-check</t>
+          <t>room.messages.spectator-win-stalemate</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>You win — your opponent lost by perpetual check</t>
+          <t>{0} won — opponent had no legal moves</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Bạn thắng vì đối thủ chiếu quẩn</t>
+          <t>{0} thắng do đối thủ hết nước đi</t>
         </is>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-lose-perpetual-check</t>
+          <t>room.messages.spectator-win-timeout</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>You lose by perpetual check</t>
+          <t>{0} won on time</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Bạn thua do chiếu quẩn</t>
+          <t>{0} thắng do đối thủ hết giờ</t>
         </is>
       </c>
     </row>
     <row r="306" ht="90" customHeight="1">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-win-per-move-timeout</t>
+          <t>room.messages.spectator-win-per-move-timeout</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>You win — your opponent ran out of move time</t>
+          <t>{0} won — opponent ran out of move time</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Bạn thắng vì đối thủ hết giờ đi một nước</t>
+          <t>{0} thắng do đối thủ hết giờ đi một nước</t>
         </is>
       </c>
     </row>
     <row r="307" ht="90" customHeight="1">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-lose-per-move-timeout</t>
+          <t>room.messages.spectator-draw</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>You lose — you ran out of move time</t>
+          <t>The game ended in a draw</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Bạn thua do hết giờ đi một nước</t>
+          <t>Ván đấu kết thúc với tỉ số hòa</t>
         </is>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>room.messages.spectator-win-checkmate</t>
+          <t>room.messages.back-to-room</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>{0} won by checkmate</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>{0} thắng do chiếu bí</t>
+          <t>Quay lại phòng</t>
         </is>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>room.messages.spectator-win-stalemate</t>
+          <t>room.messages.auto-back-countdown</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>{0} won — opponent had no legal moves</t>
+          <t>{0}. Press the back button to return to the room. You will be automatically returned in {1}s</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>{0} thắng do đối thủ hết nước đi</t>
+          <t>{0}. Bấm nút quay lại để quay lại room. Bạn sẽ tự động quay lại trong {1}s</t>
         </is>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>room.messages.spectator-win-timeout</t>
+          <t>room.notifications.joined</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>{0} won on time</t>
+          <t>{0} joined the room</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>{0} thắng do đối thủ hết giờ</t>
+          <t>{0} đã vào phòng</t>
         </is>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>room.messages.spectator-win-per-move-timeout</t>
+          <t>room.notifications.left</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>{0} won — opponent ran out of move time</t>
+          <t>{0} left the room</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>{0} thắng do đối thủ hết giờ đi một nước</t>
+          <t>{0} đã rời phòng</t>
         </is>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>room.messages.spectator-win-perpetual-check</t>
+          <t>room.settings.title</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>{0} won — opponent lost by perpetual check</t>
+          <t>Room Settings</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>{0} thắng do đối thủ chiếu quẩn</t>
+          <t>Cài đặt phòng</t>
         </is>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>room.messages.spectator-draw</t>
+          <t>room.settings.room-name</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>The game ended in a draw</t>
+          <t>Room name</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Ván đấu kết thúc với tỉ số hòa</t>
+          <t>Tên phòng</t>
         </is>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>room.messages.back-to-room</t>
+          <t>room.settings.players</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Back to room</t>
+          <t>Spectators</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Quay lại phòng</t>
+          <t>Người xem</t>
         </is>
       </c>
     </row>
     <row r="315" ht="54" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>room.messages.auto-back-countdown</t>
+          <t>room.settings.save</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>{0}. Press the back button to return to the room. You will be automatically returned in {1}s</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>{0}. Bấm nút quay lại để quay lại room. Bạn sẽ tự động quay lại trong {1}s</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>room.notifications.joined</t>
+          <t>room-invite.messages.title</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>{0} joined the room</t>
+          <t>Room Invitation</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>{0} đã vào phòng</t>
+          <t>Lời mời vào phòng</t>
         </is>
       </c>
     </row>
     <row r="317" ht="90" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>room.notifications.left</t>
+          <t>start-game.messages.success</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>{0} left the room</t>
+          <t>Game started successfully</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>{0} đã rời phòng</t>
+          <t>Bắt đầu trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>room.settings.title</t>
+          <t>start-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Room Settings</t>
+          <t>Internal server error while starting game</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="319" ht="36" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>room.settings.room-name</t>
+          <t>start-game.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Room name</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>room.settings.players</t>
+          <t>start-game.messages.invalid-difficulty</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Spectators</t>
+          <t>Bot difficulty must be between 1 and 5</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Người xem</t>
+          <t>Độ khó của bot phải từ 1 đến 5</t>
         </is>
       </c>
     </row>
     <row r="321" ht="72" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>room.settings.save</t>
+          <t>start-game.messages.room-not-found</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>room-invite.messages.title</t>
+          <t>start-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Room Invitation</t>
+          <t>Only the room host can start the game</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Lời mời vào phòng</t>
+          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="323" ht="54" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.success</t>
+          <t>start-game.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Game started successfully</t>
+          <t>You do not have enough balance to start a game with this bet</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu trò chơi thành công</t>
+          <t>Bạn không còn đủ amount để start room</t>
         </is>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.internal-server-error</t>
+          <t>start-game.messages.requester-must-pick-team</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while starting game</t>
+          <t>You must select a team before starting a game with bot</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
+          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
         </is>
       </c>
     </row>
     <row r="325" ht="72" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-room-id</t>
+          <t>update-room.messages.success</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Room updated successfully</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Cập nhật phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-difficulty</t>
+          <t>update-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Bot difficulty must be between 1 and 5</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Độ khó của bot phải từ 1 đến 5</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="327" ht="90" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.room-not-found</t>
+          <t>update-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Invalid room ID</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>ID phòng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.forbidden</t>
+          <t>update-room.messages.invalid-time-limit</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Only the room host can start the game</t>
+          <t>Invalid time limit</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
+          <t>Thời gian không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="329" ht="72" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.insufficient-amount</t>
+          <t>update-room.messages.invalid-time-increment</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to start a game with this bet</t>
+          <t>Invalid bonus per move</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để start room</t>
+          <t>Thời gian cộng mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="330" ht="54" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.requester-must-pick-team</t>
+          <t>update-room.messages.invalid-time-per-move</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>You must select a team before starting a game with bot</t>
+          <t>Invalid time per move</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
+          <t>Thời gian mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="331" ht="54" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.success</t>
+          <t>update-room.messages.name-required</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Room updated successfully</t>
+          <t>Room name is required</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật phòng thành công</t>
+          <t>Tên phòng không được để trống</t>
         </is>
       </c>
     </row>
     <row r="332" ht="54" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.internal-server-error</t>
+          <t>update-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="333" ht="90" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-room-id</t>
+          <t>update-room.messages.forbidden</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Invalid room ID</t>
+          <t>You are not the host of this room</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>ID phòng không hợp lệ</t>
+          <t>Bạn không phải chủ phòng</t>
         </is>
       </c>
     </row>
     <row r="334" ht="54" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-time-limit</t>
+          <t>draw-game.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Invalid time limit</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Thời gian không hợp lệ</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="335" ht="36" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-time-increment</t>
+          <t>draw-game.messages.game-not-found</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Invalid bonus per move</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Thời gian cộng mỗi nước không hợp lệ</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-time-per-move</t>
+          <t>draw-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>Invalid time per move</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Thời gian mỗi nước không hợp lệ</t>
+          <t>Bạn không có trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="337" ht="36" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.name-required</t>
+          <t>draw-game.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Room name is required</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng không được để trống</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="338" ht="36" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.room-not-found</t>
+          <t>draw-game.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="339" ht="72" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.forbidden</t>
+          <t>draw-game.messages.success</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>You are not the host of this room</t>
+          <t>Draw game successfully</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải chủ phòng</t>
+          <t>Hòa cờ thành công</t>
         </is>
       </c>
     </row>
     <row r="340" ht="54" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.invalid-game-id</t>
+          <t>draw-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="341" ht="54" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-not-found</t>
+          <t>surrender.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="342" ht="90" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.forbidden</t>
+          <t>surrender.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Bạn không có trong phòng này</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="343" ht="54" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-history-not-found</t>
+          <t>surrender.messages.game-not-found</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-already-finished</t>
+          <t>surrender.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.success</t>
+          <t>surrender.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Draw game successfully</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="346" ht="36" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.internal-server-error</t>
+          <t>surrender.messages.invalid-surrender-player</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You are not a player in this game</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.game-already-finished</t>
+          <t>surrender.messages.opponent-not-found</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>Opponent not found</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Không tìm thấy đối thủ</t>
         </is>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.game-history-not-found</t>
+          <t>surrender.messages.success</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>Surrendered</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Đã đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="349" ht="36" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.game-not-found</t>
+          <t>undo.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.internal-server-error</t>
+          <t>undo.messages.unauthorized</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Unauthorized</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không được phép truy cập</t>
         </is>
       </c>
     </row>
     <row r="351" ht="36" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-game-id</t>
+          <t>undo.messages.game-not-found</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-surrender-player</t>
+          <t>undo.messages.not-in-game</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>You are not a player in this game</t>
+          <t>You are not part of this game</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -6320,1702 +6320,1630 @@
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.opponent-not-found</t>
+          <t>undo.messages.not-in-room</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Opponent not found</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy đối thủ</t>
+          <t>Bạn không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.success</t>
+          <t>undo.messages.pve-only</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Surrendered</t>
+          <t>Undo is only available in PvE rooms</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Đã đầu hàng</t>
+          <t>Hoàn tác chỉ khả dụng trong phòng PvE</t>
         </is>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.invalid-game-id</t>
+          <t>undo.messages.spectator-cannot-undo</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Spectators cannot undo moves</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Người xem không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.unauthorized</t>
+          <t>undo.messages.no-moves</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Unauthorized</t>
+          <t>No moves to undo</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Không được phép truy cập</t>
+          <t>Không có nước đi để hoàn tác</t>
         </is>
       </c>
     </row>
     <row r="357" ht="17" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.game-not-found</t>
+          <t>undo.messages.delete-failed</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Failed to undo move</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-game</t>
+          <t>undo.messages.undo-limit-exceeded</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>You are not part of this game</t>
+          <t>Maximum 3 undo per game exceeded</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
         </is>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-room</t>
+          <t>undo.messages.success</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Move undone successfully</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Bạn không trong phòng này</t>
+          <t>Hoàn tác nước đi thành công</t>
         </is>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.pve-only</t>
+          <t>undo.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>Undo is only available in PvE rooms</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Hoàn tác chỉ khả dụng trong phòng PvE</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.spectator-cannot-undo</t>
+          <t>player-history.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>Spectators cannot undo moves</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>Người xem không thể hoàn tác nước đi</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.no-moves</t>
+          <t>player-history.messages.success</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>No moves to undo</t>
+          <t>Fetch game history successfully</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Không có nước đi để hoàn tác</t>
+          <t>Lấy lịch sử trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.delete-failed</t>
+          <t>validate-token.messages.success</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>Failed to undo move</t>
+          <t>Token is valid</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Không thể hoàn tác nước đi</t>
+          <t>Token hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="364" ht="17" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.undo-limit-exceeded</t>
+          <t>guide.section.objective</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Maximum 3 undo per game exceeded</t>
+          <t>Objective of the game</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
+          <t>Mục tiêu của trò chơi</t>
         </is>
       </c>
     </row>
     <row r="365" ht="17" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.success</t>
+          <t>guide.section.pieces</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>Move undone successfully</t>
+          <t>Pieces</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Hoàn tác nước đi thành công</t>
+          <t>Quân cờ</t>
         </is>
       </c>
     </row>
     <row r="366" ht="17" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.internal-server-error</t>
+          <t>guide.section.moving-pieces</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Moving pieces</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Đi quân</t>
         </is>
       </c>
     </row>
     <row r="367" ht="17" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.invalid-user-id</t>
+          <t>guide.section.capturing</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>Capturing</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Bắt quân</t>
         </is>
       </c>
     </row>
     <row r="368" ht="17" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.success</t>
+          <t>guide.section.check</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>Fetch game history successfully</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Lấy lịch sử trò chơi thành công</t>
+          <t>Chiếu tướng</t>
         </is>
       </c>
     </row>
     <row r="369" ht="17" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>validate-token.messages.success</t>
+          <t>guide.section.result</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>Token is valid</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Token hợp lệ</t>
+          <t>Kết quả</t>
         </is>
       </c>
     </row>
     <row r="370" ht="17" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>guide.section.objective</t>
+          <t>guide.table.piece</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Objective of the game</t>
+          <t>Piece</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu của trò chơi</t>
+          <t>Quân</t>
         </is>
       </c>
     </row>
     <row r="371" ht="17" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>guide.section.pieces</t>
+          <t>guide.table.symbol</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Pieces</t>
+          <t>Symbol</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Quân cờ</t>
+          <t>Ký hiệu</t>
         </is>
       </c>
     </row>
     <row r="372" ht="17" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>guide.section.moving-pieces</t>
+          <t>guide.table.quantity</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Moving pieces</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Đi quân</t>
+          <t>Số lượng</t>
         </is>
       </c>
     </row>
     <row r="373" ht="17" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>guide.section.capturing</t>
+          <t>guide.objective.paragraph1</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Capturing</t>
+          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân</t>
+          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
         </is>
       </c>
     </row>
     <row r="374" ht="17" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>guide.section.check</t>
+          <t>guide.pieces.paragraph1</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Chiếu tướng</t>
+          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
         </is>
       </c>
     </row>
     <row r="375" ht="17" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>guide.section.result</t>
+          <t>guide.piece.general</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Kết quả</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="376" ht="17" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>guide.table.piece</t>
+          <t>guide.piece.advisor</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Piece</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Quân</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="377" ht="17" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>guide.table.symbol</t>
+          <t>guide.piece.elephant</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>Symbol</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>Ký hiệu</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="378" ht="17" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>guide.table.quantity</t>
+          <t>guide.piece.chariot</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Số lượng</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="379" ht="17" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>guide.objective.paragraph1</t>
+          <t>guide.piece.horse</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="380" ht="17" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>guide.pieces.paragraph1</t>
+          <t>guide.piece.cannon</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="381" ht="17" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.general</t>
+          <t>guide.piece.soldier</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>guide.piece.advisor</t>
+          <t>guide.moving-pieces.paragraph1</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>guide.piece.elephant</t>
+          <t>guide.general.paragraph1</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>guide.piece.chariot</t>
+          <t>guide.general.paragraph2</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>guide.piece.horse</t>
+          <t>guide.advisor.paragraph1</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>guide.piece.cannon</t>
+          <t>guide.advisor.paragraph2</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>guide.piece.soldier</t>
+          <t>guide.elephant.paragraph1</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>guide.moving-pieces.paragraph1</t>
+          <t>guide.elephant.paragraph2</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
+          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>guide.general.paragraph1</t>
+          <t>guide.chariot.paragraph1</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>guide.general.paragraph2</t>
+          <t>guide.chariot.paragraph2</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
+          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph1</t>
+          <t>guide.horse.paragraph1</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph2</t>
+          <t>guide.horse.paragraph2</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
+          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
+          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph1</t>
+          <t>guide.cannon.paragraph1</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph2</t>
+          <t>guide.cannon.paragraph2</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
+          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph1</t>
+          <t>guide.soldier.paragraph1</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph2</t>
+          <t>guide.soldier.paragraph2</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
+          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
+          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph1</t>
+          <t>guide.capturing.paragraph1</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph2</t>
+          <t>guide.capturing.paragraph2</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
+          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
+          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph1</t>
+          <t>guide.capturing.paragraph3</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph2</t>
+          <t>guide.check.paragraph1</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
+          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
+          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph1</t>
+          <t>guide.check.paragraph2</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph2</t>
+          <t>guide.check.paragraph3</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
+          <t>Move the General to another position to escape check</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
+          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph1</t>
+          <t>guide.check.paragraph4</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
+          <t>Capture the checking piece</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
+          <t>Bắt quân đang chiếu</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph2</t>
+          <t>guide.check.paragraph5</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
+          <t>Block the checking line with another piece to protect the General</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
+          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph3</t>
+          <t>guide.check.paragraph6</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
+          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
+          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>guide.check.paragraph1</t>
+          <t>guide.result.paragraph1</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
+          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
+          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>guide.check.paragraph2</t>
+          <t>guide.result.paragraph2</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
+          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
+          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>guide.check.paragraph3</t>
+          <t>guide.result.paragraph3</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Move the General to another position to escape check</t>
+          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
+          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>guide.check.paragraph4</t>
+          <t>guide.result.paragraph4</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Capture the checking piece</t>
+          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Bắt quân đang chiếu</t>
+          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>guide.check.paragraph5</t>
+          <t>guide.result.paragraph5</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Block the checking line with another piece to protect the General</t>
+          <t>Within 50 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
+          <t>Trong vòng 50 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>guide.check.paragraph6</t>
+          <t>extra-money.title</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>guide.result.paragraph1</t>
+          <t>extra-money.tab.lucky-wheel</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
+          <t>Lucky Wheel</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
+          <t>Vòng Quay May Mắn</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>guide.result.paragraph2</t>
+          <t>extra-money.tab.bonus-coin</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>Bonus Coin</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Xu Thưởng</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>guide.result.paragraph3</t>
+          <t>extra-money.tab.daily-bonus</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>Daily Bonus</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Thưởng hàng ngày</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>guide.result.paragraph4</t>
+          <t>extra-money.bonus-coin.subtitle</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>Watch a short video to earn free coin</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Xem video ngắn để nhận xu miễn phí</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>guide.result.paragraph5</t>
+          <t>extra-money.bonus-coin.next-in</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Within 50 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>Next in:</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Trong vòng 50 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Lượt kế tiếp:</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>extra-money.title</t>
+          <t>extra-money.bonus-coin.collect</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Collect</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Kiếm tiền</t>
+          <t>Thu thập</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>extra-money.tab.lucky-wheel</t>
+          <t>extra-money.bonus-coin.watch-video</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Lucky Wheel</t>
+          <t>Watch video</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Vòng Quay May Mắn</t>
+          <t>Xem video</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>extra-money.tab.bonus-coin</t>
+          <t>extra-money.daily-bonus.subtitle</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Bonus Coin</t>
+          <t>Login 7 days in a row to earn 4000 coin</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Xu Thưởng</t>
+          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>extra-money.tab.daily-bonus</t>
+          <t>extra-money.daily-bonus.day</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Daily Bonus</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Thưởng hàng ngày</t>
+          <t>Ngày</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.subtitle</t>
+          <t>extra-money.reward-ad.loading</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Watch a short video to earn free coin</t>
+          <t>Loading ad...</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Xem video ngắn để nhận xu miễn phí</t>
+          <t>Đang tải quảng cáo...</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.next-in</t>
+          <t>extra-money.reward-ad.error</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Next in:</t>
+          <t>Could not load the ad. Please try again.</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Lượt kế tiếp:</t>
+          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.collect</t>
+          <t>extra-money.reward-ad.retry</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Collect</t>
+          <t>Try again</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Thu thập</t>
+          <t>Thử lại</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.watch-video</t>
+          <t>extra-money.reward-ad.close</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Watch video</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Xem video</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.subtitle</t>
+          <t>profile.button.save</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Login 7 days in a row to earn 4000 coin</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.day</t>
+          <t>profile.button.cancel</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Ngày</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.loading</t>
+          <t>change-password.title</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Loading ad...</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Đang tải quảng cáo...</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.error</t>
+          <t>change-password.current.label</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Could not load the ad. Please try again.</t>
+          <t>Current password</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
+          <t>Mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.retry</t>
+          <t>change-password.current.placeholder</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Try again</t>
+          <t>Enter current password</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Nhập mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.close</t>
+          <t>change-password.new.label</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>New password</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>profile.button.save</t>
+          <t>change-password.new.placeholder</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Enter new password</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Nhập mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>profile.button.cancel</t>
+          <t>change-password.confirm.label</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Confirm new password</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Xác nhận mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>change-password.title</t>
+          <t>change-password.confirm.placeholder</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Re-enter new password</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Nhập lại mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>change-password.current.label</t>
+          <t>change-password.confirm.mismatch</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Current password</t>
+          <t>Passwords do not match</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại</t>
+          <t>Mật khẩu xác nhận không khớp</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>change-password.current.placeholder</t>
+          <t>change-password.show</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Enter current password</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu hiện tại</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>change-password.new.label</t>
+          <t>change-password.hide</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Mật khẩu mới</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>change-password.new.placeholder</t>
+          <t>change-password.submit</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Enter new password</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu mới</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>change-password.confirm.label</t>
+          <t>change-password.submitting</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Confirm new password</t>
+          <t>Changing...</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu mới</t>
+          <t>Đang đổi...</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>change-password.confirm.placeholder</t>
+          <t>change-password.messages.success</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Re-enter new password</t>
+          <t>Password changed successfully</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Nhập lại mật khẩu mới</t>
+          <t>Đổi mật khẩu thành công</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>change-password.confirm.mismatch</t>
+          <t>change-password.messages.missing-fields</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Passwords do not match</t>
+          <t>Please fill in all fields</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp</t>
+          <t>Vui lòng nhập đầy đủ thông tin</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>change-password.show</t>
+          <t>change-password.messages.weak-password</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>New password does not meet the requirements</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Mật khẩu mới không đạt yêu cầu</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>change-password.hide</t>
+          <t>change-password.messages.same-as-current</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>New password must be different from the current one</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>change-password.submit</t>
+          <t>change-password.messages.incorrect-current-password</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Current password is incorrect</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Mật khẩu hiện tại không đúng</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>change-password.submitting</t>
+          <t>change-password.messages.user-not-found</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Changing...</t>
+          <t>User not found</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Đang đổi...</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>change-password.messages.success</t>
+          <t>change-password.messages.unauthorized</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Password changed successfully</t>
+          <t>Session expired. Please sign in again.</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu thành công</t>
+          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>change-password.messages.missing-fields</t>
+          <t>change-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Please fill in all fields</t>
+          <t>Something went wrong. Please try again.</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Vui lòng nhập đầy đủ thông tin</t>
+          <t>Đã có lỗi xảy ra. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>change-password.messages.weak-password</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>New password does not meet the requirements</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>Mật khẩu mới không đạt yêu cầu</t>
-        </is>
-      </c>
+      <c r="A447" t="inlineStr"/>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>change-password.messages.same-as-current</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>New password must be different from the current one</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
-        </is>
-      </c>
+      <c r="A448" t="inlineStr"/>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>change-password.messages.incorrect-current-password</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>Current password is incorrect</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>Mật khẩu hiện tại không đúng</t>
-        </is>
-      </c>
+      <c r="A449" t="inlineStr"/>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>change-password.messages.user-not-found</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>User not found</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>Không tìm thấy người dùng</t>
-        </is>
-      </c>
+      <c r="A450" t="inlineStr"/>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>change-password.messages.unauthorized</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>Session expired. Please sign in again.</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
-        </is>
-      </c>
+      <c r="A451" t="inlineStr"/>
+      <c r="B451" t="inlineStr"/>
+      <c r="C451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>change-password.messages.internal-server-error</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>Something went wrong. Please try again.</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>Đã có lỗi xảy ra. Vui lòng thử lại.</t>
-        </is>
-      </c>
+      <c r="A452" t="inlineStr"/>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr"/>
@@ -8081,36 +8009,6 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr"/>
       <c r="C465" t="inlineStr"/>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr"/>
-      <c r="B466" t="inlineStr"/>
-      <c r="C466" t="inlineStr"/>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr"/>
-      <c r="B467" t="inlineStr"/>
-      <c r="C467" t="inlineStr"/>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr"/>
-      <c r="B468" t="inlineStr"/>
-      <c r="C468" t="inlineStr"/>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr"/>
-      <c r="B469" t="inlineStr"/>
-      <c r="C469" t="inlineStr"/>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr"/>
-      <c r="B470" t="inlineStr"/>
-      <c r="C470" t="inlineStr"/>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr"/>
-      <c r="B471" t="inlineStr"/>
-      <c r="C471" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tools/languages.xlsx
+++ b/Tools/languages.xlsx
@@ -325,7 +325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C465"/>
+  <dimension ref="A1:C472"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2325,823 +2325,823 @@
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>game.label.win</t>
+          <t>game.piece.queen</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Win</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Thắng</t>
+          <t>Hậu</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>game.label.draw</t>
+          <t>game.piece.rook</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Rook</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Hoà</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>game.label.lose</t>
+          <t>game.piece.bishop</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Lose</t>
+          <t>Bishop</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Thua</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.title</t>
+          <t>game.piece.knight</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Select Bot Difficulty</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Chọn độ khó của Bot</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.beginner</t>
+          <t>game.promotion.title</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Pawn promotion</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Mới bắt đầu</t>
+          <t>Phong cấp quân tốt</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.amateur</t>
+          <t>game.promotion.subtitle</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Amateur</t>
+          <t>Choose the piece to promote to</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Nghiệp dư</t>
+          <t>Chọn quân thay thế cho tốt</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.intermediate</t>
+          <t>game.promotion.cancel</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Cancel move</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Trung bình</t>
+          <t>Huỷ nước đi</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.advanced</t>
+          <t>game.label.win</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Win</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Nâng cao</t>
+          <t>Thắng</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>room.bot-difficulty.master</t>
+          <t>game.label.draw</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Lão luyện</t>
+          <t>Hoà</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>login.page.title</t>
+          <t>game.label.lose</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Lose</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Thua</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>login.form.title</t>
+          <t>room.bot-difficulty.title</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Select Bot Difficulty</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Chọn độ khó của Bot</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>login.username.label</t>
+          <t>room.bot-difficulty.beginner</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Beginner</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Mới bắt đầu</t>
         </is>
       </c>
     </row>
     <row r="130" ht="36" customHeight="1">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>login.username.placeholder</t>
+          <t>room.bot-difficulty.amateur</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Amateur</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Nghiệp dư</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>login.password.label</t>
+          <t>room.bot-difficulty.intermediate</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Intermediate</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Trung bình</t>
         </is>
       </c>
     </row>
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>login.password.placeholder</t>
+          <t>room.bot-difficulty.advanced</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Advanced</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Nâng cao</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>login.password.show</t>
+          <t>room.bot-difficulty.master</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Lão luyện</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>login.password.hide</t>
+          <t>login.page.title</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="135" ht="36" customHeight="1">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>login.form.error1</t>
+          <t>login.form.title</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login failed. Please check your credentials </t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>login.form.forgot-password</t>
+          <t>login.username.label</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>login.form.register</t>
+          <t>login.username.placeholder</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>login.form.submit</t>
+          <t>login.password.label</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>login.form.or</t>
+          <t>login.password.placeholder</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>hoặc</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>login.google.load-error</t>
+          <t>login.password.show</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Could not load Google Sign-In</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Không tải được đăng nhập Google</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>login.facebook.button</t>
+          <t>login.password.hide</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Sign-in with Facebook</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với Facebook</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="142" ht="36" customHeight="1">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>login.messages.incorrect-login</t>
+          <t>login.form.error1</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Invalid username or password</t>
+          <t xml:space="preserve">Login failed. Please check your credentials </t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
+          <t>Đăng nhập không thành công. Hãy kiểm tra lại</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>login.messages.internal-server-error</t>
+          <t>login.form.forgot-password</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>login.messages.missing-credentials</t>
+          <t>login.form.register</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Username and password are required</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng và mật khẩu là bắt buộc</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>login.messages.success</t>
+          <t>login.form.submit</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Login successful</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>notfound.title</t>
+          <t>login.form.or</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Page Not Found</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Trang không tìm thấy</t>
+          <t>hoặc</t>
         </is>
       </c>
     </row>
     <row r="147" ht="36" customHeight="1">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>notfound.description</t>
+          <t>login.google.load-error</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>The page you are looking for does not exist or has been moved.</t>
+          <t>Could not load Google Sign-In</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
+          <t>Không tải được đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>notfound.home</t>
+          <t>login.facebook.button</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Go to Home</t>
+          <t>Sign-in with Facebook</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Về trang chủ</t>
+          <t>Đăng nhập với Facebook</t>
         </is>
       </c>
     </row>
     <row r="149" ht="36" customHeight="1">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>notfound.back</t>
+          <t>login.messages.incorrect-login</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Go Back</t>
+          <t>Invalid username or password</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Quay lại</t>
+          <t>Tên người dùng hoặc mật khẩu không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.error1</t>
+          <t>login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Confirm password does not match password</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.label</t>
+          <t>login.messages.missing-credentials</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Username and password are required</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Tên người dùng và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>register.confirm-password.placeholder</t>
+          <t>login.messages.success</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Login successful</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.label</t>
+          <t>notfound.title</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>Page Not Found</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Trang không tìm thấy</t>
         </is>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>register.display-name.placeholder</t>
+          <t>notfound.description</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Display name</t>
+          <t>The page you are looking for does not exist or has been moved.</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Tên hiển thị</t>
+          <t>Trang bạn tìm kiếm không tồn tại hoặc đã được di chuyển.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>register.email.error1</t>
+          <t>notfound.home</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Go to Home</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Về trang chủ</t>
         </is>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>register.email.label</t>
+          <t>notfound.back</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Go Back</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Quay lại</t>
         </is>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>register.email.placeholder</t>
+          <t>register.confirm-password.error1</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Confirm password does not match password</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Mật khẩu xác nhận không khớp với mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>register.form.login</t>
+          <t>register.confirm-password.label</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="159" ht="36" customHeight="1">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>register.form.submit</t>
+          <t>register.confirm-password.placeholder</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Confirm Password</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Xác nhận mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>register.form.success</t>
+          <t>register.display-name.label</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Registration successful. Redirecting to login...</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký thành công. Đang chuyển hướng...</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>register.form.title</t>
+          <t>register.display-name.placeholder</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Display name</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Tên hiển thị</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>register.gender.female</t>
+          <t>register.email.error1</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>register.gender.label</t>
+          <t>register.email.label</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Giới tính</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="164" ht="36" customHeight="1">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>register.gender.male</t>
+          <t>register.email.placeholder</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>register.gender.select</t>
+          <t>register.form.login</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Select gender</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Chọn giới tính</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>register.page.title</t>
+          <t>register.form.submit</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -3158,959 +3158,959 @@
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>register.password.error1</t>
+          <t>register.form.success</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
+          <t>Registration successful. Redirecting to login...</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
+          <t>Đăng ký thành công. Đang chuyển hướng...</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>register.password.hide</t>
+          <t>register.form.title</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>register.password.label</t>
+          <t>register.gender.female</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Nữ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>register.password.placeholder</t>
+          <t>register.gender.label</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Giới tính</t>
         </is>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>register.password.show</t>
+          <t>register.gender.male</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Nam</t>
         </is>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>register.username.error1</t>
+          <t>register.gender.select</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
+          <t>Select gender</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
+          <t>Chọn giới tính</t>
         </is>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>register.username.label</t>
+          <t>register.page.title</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Đăng ký</t>
         </is>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>register.username.placeholder</t>
+          <t>register.password.error1</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Password must be at least 8 characters and contain uppercase, lowercase, number, and special character</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng</t>
+          <t>Mật khẩu phải có ít nhất 8 ký tự và chứa chữ hoa, chữ thường, số và ký tự đặc biệt</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.page.title</t>
+          <t>register.password.hide</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="176" ht="36" customHeight="1">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.title</t>
+          <t>register.password.label</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.login</t>
+          <t>register.password.placeholder</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Về trang đăng nhập</t>
+          <t>Mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.submit</t>
+          <t>register.password.show</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.success</t>
+          <t>register.username.error1</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Check your email for reset password details.</t>
+          <t>User name must contain only alphanumeric characters, underscore, and dot</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
+          <t>Tên người dùng chỉ chứa ký tự chữ số, dấu gạch dưới và dấu chấm</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.form.error1</t>
+          <t>register.username.label</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Forgot password failed.</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Quên mật khẩu không thành công.</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>reset-password.page.title</t>
+          <t>register.username.placeholder</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Tên người dùng</t>
         </is>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.title</t>
+          <t>forgot-password.page.title</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Reset your password</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu của bạn</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.submit</t>
+          <t>forgot-password.form.title</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.error1</t>
+          <t>forgot-password.form.login</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>An error occurred while resetting your password. Please try again.</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
+          <t>Về trang đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="185" ht="36" customHeight="1">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.invalid-token</t>
+          <t>forgot-password.form.submit</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Forgot password</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Quên mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>reset-password.form.success</t>
+          <t>forgot-password.form.success</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Password reset successfully. Redirecting to login...</t>
+          <t>Check your email for reset password details.</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
+          <t>Hãy kiểm tra email để xem thông tin đặt lại mật khẩu.</t>
         </is>
       </c>
     </row>
     <row r="187" ht="36" customHeight="1">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>reset-password.action.back-to-login</t>
+          <t>forgot-password.form.error1</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Back to login</t>
+          <t>Forgot password failed.</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Quay lại trang chủ</t>
+          <t>Quên mật khẩu không thành công.</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.invalid-token-payload</t>
+          <t>reset-password.page.title</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Invalid token payload</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Payload của token không hợp lệ</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.session-not-found</t>
+          <t>reset-password.form.title</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Session not found</t>
+          <t>Reset your password</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phiên</t>
+          <t>Đặt lại mật khẩu của bạn</t>
         </is>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-expired</t>
+          <t>reset-password.form.submit</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Token is expired</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Token đã hết hạn</t>
+          <t>Đặt lại mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-invalid</t>
+          <t>reset-password.form.error1</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Token is invalid</t>
+          <t>An error occurred while resetting your password. Please try again.</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Token không hợp lệ</t>
+          <t>Có lỗi xảy ra khi đặt lại mật khẩu. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-required</t>
+          <t>reset-password.form.invalid-token</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Token not provided</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Token không được cung cấp</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-subject-mismatch</t>
+          <t>reset-password.form.success</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Token subject mismatch</t>
+          <t>Password reset successfully. Redirecting to login...</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Token chủ đề không khớp</t>
+          <t>Đặt lại mật khẩu thành công. Đang chuyển hướng đến đăng nhập...</t>
         </is>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>auth-middleware.messages.token-validation-failed</t>
+          <t>reset-password.action.back-to-login</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Token validation failed</t>
+          <t>Back to login</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Xác thực token không thành công</t>
+          <t>Quay lại trang chủ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.insufficient-amount</t>
+          <t>auth-middleware.messages.invalid-token-payload</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to create a room with this bet</t>
+          <t>Invalid token payload</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
+          <t>Payload của token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.internal-server-error</t>
+          <t>auth-middleware.messages.session-not-found</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while creating room</t>
+          <t>Session not found</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
+          <t>Không tìm thấy phiên</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-bet-amount</t>
+          <t>auth-middleware.messages.token-expired</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Bet amount is required and must be one of the acceptable values</t>
+          <t>Token is expired</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
+          <t>Token đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-time-limit</t>
+          <t>auth-middleware.messages.token-invalid</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Invalid time limit</t>
+          <t>Token is invalid</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Thời gian không hợp lệ</t>
+          <t>Token không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-time-increment</t>
+          <t>auth-middleware.messages.token-required</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Invalid bonus per move</t>
+          <t>Token not provided</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Thời gian cộng mỗi nước không hợp lệ</t>
+          <t>Token không được cung cấp</t>
         </is>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-time-per-move</t>
+          <t>auth-middleware.messages.token-subject-mismatch</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Invalid time per move</t>
+          <t>Token subject mismatch</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Thời gian mỗi nước không hợp lệ</t>
+          <t>Token chủ đề không khớp</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-redFirst</t>
+          <t>auth-middleware.messages.token-validation-failed</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' must be a boolean</t>
+          <t>Token validation failed</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>'redFirst' phải là giá trị boolean</t>
+          <t>Xác thực token không thành công</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.invalid-team-name</t>
+          <t>create-room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Team name must be either 'red', 'black', or null</t>
+          <t>You do not have enough balance to create a room with this bet</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Tên đội phải là 'red', 'black' hoặc null</t>
+          <t>Bạn không còn đủ amount để tạo phòng với mức cược này</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.name-required</t>
+          <t>create-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Room name (tableName) is required and must not be empty</t>
+          <t>Internal server error while creating room</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
+          <t>Lỗi máy chủ nội bộ khi tạo phòng</t>
         </is>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>create-room.messages.room-created</t>
+          <t>create-room.messages.invalid-bet-amount</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Room created successfully</t>
+          <t>Bet amount is required and must be one of the acceptable values</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Phòng được tạo thành công</t>
+          <t>Số tiền cược là bắt buộc và phải là một trong các giá trị được chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.internal-server-error</t>
+          <t>create-room.messages.invalid-time-limit</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Invalid time limit</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thời gian không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.invalid-status</t>
+          <t>create-room.messages.invalid-time-increment</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Query parameter 'status' must be an integer</t>
+          <t>Invalid bonus per move</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Tham số truy vấn 'status' phải là số nguyên</t>
+          <t>Thời gian cộng mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>fetch-rooms.messages.success</t>
+          <t>create-room.messages.invalid-time-per-move</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Fetch rooms successfully</t>
+          <t>Invalid time per move</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Lấy phòng thành công</t>
+          <t>Thời gian mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-not-found</t>
+          <t>create-room.messages.invalid-redFirst</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Email does not exist</t>
+          <t>'redFirst' must be a boolean</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Email không tồn tại</t>
+          <t>'redFirst' phải là giá trị boolean</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.email-service-not-configured</t>
+          <t>create-room.messages.invalid-team-name</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Email service is not configured</t>
+          <t>Team name must be either 'red', 'black', or null</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Dịch vụ email chưa được cấu hình</t>
+          <t>Tên đội phải là 'red', 'black' hoặc null</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.internal-server-error</t>
+          <t>create-room.messages.name-required</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Room name (tableName) is required and must not be empty</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Tên phòng (tableName) là bắt buộc và không được để trống</t>
         </is>
       </c>
     </row>
     <row r="211" ht="36" customHeight="1">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.invalid-email-format</t>
+          <t>create-room.messages.room-created</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>Room created successfully</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Định dạng email không hợp lệ</t>
+          <t>Phòng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.missing-email</t>
+          <t>fetch-rooms.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Email is required</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Email là bắt buộc</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>forgot-password.messages.success</t>
+          <t>fetch-rooms.messages.invalid-status</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Forgot password email sent</t>
+          <t>Query parameter 'status' must be an integer</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Email đặt lại mật khẩu đã được gửi</t>
+          <t>Tham số truy vấn 'status' phải là số nguyên</t>
         </is>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.internal-server-error</t>
+          <t>fetch-rooms.messages.success</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Fetch rooms successfully</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Lấy phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-team</t>
+          <t>forgot-password.messages.email-not-found</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
+          <t>Email does not exist</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
+          <t>Email không tồn tại</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.invalid-room-id</t>
+          <t>forgot-password.messages.email-service-not-configured</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Email service is not configured</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Dịch vụ email chưa được cấu hình</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.room-not-found</t>
+          <t>forgot-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.success</t>
+          <t>forgot-password.messages.invalid-email-format</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Successfully joined the room</t>
+          <t>Invalid email format</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Tham gia phòng thành công</t>
+          <t>Định dạng email không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>join-room.messages.team-seat-occupied</t>
+          <t>forgot-password.messages.missing-email</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Selected team seat is already occupied</t>
+          <t>Email is required</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Vị trí đội đã chọn đã có người chơi</t>
+          <t>Email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.cannot-kick-self</t>
+          <t>forgot-password.messages.success</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>You cannot kick yourself</t>
+          <t>Forgot password email sent</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Bạn không thể kick chính mình</t>
+          <t>Email đặt lại mật khẩu đã được gửi</t>
         </is>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.forbidden</t>
+          <t>join-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Only the host can kick users</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.internal-server-error</t>
+          <t>join-room.messages.invalid-team</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Field 'team' must be 'red', 'black', null, or undefined</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trường 'team' phải là 'red', 'black', null hoặc không truyền</t>
         </is>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-room-id</t>
+          <t>join-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -4127,3828 +4127,3912 @@
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.invalid-user-id</t>
+          <t>join-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Field 'userId' is required and must be a positive integer</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-found</t>
+          <t>join-room.messages.success</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Successfully joined the room</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Tham gia phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.room-not-waiting</t>
+          <t>join-room.messages.team-seat-occupied</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>You can only kick users while the room is waiting</t>
+          <t>Selected team seat is already occupied</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
+          <t>Vị trí đội đã chọn đã có người chơi</t>
         </is>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.success</t>
+          <t>kick-user.messages.cannot-kick-self</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>User has been kicked</t>
+          <t>You cannot kick yourself</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Người dùng đã bị kick</t>
+          <t>Bạn không thể kick chính mình</t>
         </is>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.user-not-in-room</t>
+          <t>kick-user.messages.forbidden</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>User is not in this room</t>
+          <t>Only the host can kick users</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Người dùng không trong phòng này</t>
+          <t>Chỉ chủ phòng mới có thể kick người dùng</t>
         </is>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>kick-user.messages.you-were-kicked</t>
+          <t>kick-user.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>You have been removed from the room by the host</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.internal-server-error</t>
+          <t>kick-user.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.invalid-room-id</t>
+          <t>kick-user.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Field 'userId' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Trường 'userId' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.player-not-in-room</t>
+          <t>kick-user.messages.room-not-found</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Player is not in this room</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Người chơi không trong phòng này</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>leave-room.messages.success</t>
+          <t>kick-user.messages.room-not-waiting</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Leave room successfully</t>
+          <t>You can only kick users while the room is waiting</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Rời phòng thành công</t>
+          <t>Chỉ có thể kick người dùng khi phòng đang ở trạng thái chờ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.internal-server-error</t>
+          <t>kick-user.messages.success</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>User has been kicked</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Người dùng đã bị kick</t>
         </is>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.invalid-room-id</t>
+          <t>kick-user.messages.user-not-in-room</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Room ID must be a positive integer</t>
+          <t>User is not in this room</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>ID phòng phải là số nguyên dương</t>
+          <t>Người dùng không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.room-not-found</t>
+          <t>kick-user.messages.you-were-kicked</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>You have been removed from the room by the host</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Bạn đã bị chủ phòng đưa ra khỏi phòng</t>
         </is>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>load-room.messages.success</t>
+          <t>leave-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Load room successfully</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Tải phòng thành công</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.email-not-verified</t>
+          <t>leave-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Your Google email is not verified</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Email Google của bạn chưa được xác minh</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.failed</t>
+          <t>leave-room.messages.player-not-in-room</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Login failed</t>
+          <t>Player is not in this room</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công</t>
+          <t>Người chơi không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.internal-server-error</t>
+          <t>leave-room.messages.success</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Leave room successfully</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Rời phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.invalid-token</t>
+          <t>load-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Invalid Google credential</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Google không hợp lệ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>google-login.messages.missing-credential</t>
+          <t>load-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Google credential is required</t>
+          <t>Room ID must be a positive integer</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Google</t>
+          <t>ID phòng phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.missing-token</t>
+          <t>load-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.invalid-token</t>
+          <t>load-room.messages.success</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>Load room successfully</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Tải phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.not-linked</t>
+          <t>google-login.messages.email-not-verified</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
+          <t>Your Google email is not verified</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
+          <t>Email Google của bạn chưa được xác minh</t>
         </is>
       </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>facebook-login.messages.internal-server-error</t>
+          <t>google-login.messages.failed</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Login failed</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Đăng nhập không thành công</t>
         </is>
       </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.missing-token</t>
+          <t>google-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Facebook token is required</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Thiếu thông tin đăng nhập Facebook</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.invalid-token</t>
+          <t>google-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Invalid Facebook token</t>
+          <t>Invalid Google credential</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
+          <t>Thông tin đăng nhập Google không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked</t>
+          <t>google-login.messages.missing-credential</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Facebook linked successfully</t>
+          <t>Google credential is required</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Đã liên kết Facebook</t>
+          <t>Thiếu thông tin đăng nhập Google</t>
         </is>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-linked</t>
+          <t>facebook-login.messages.missing-token</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to your account</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.linked-to-other</t>
+          <t>facebook-login.messages.invalid-token</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>This Facebook account is already linked to another account</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.already-has-facebook</t>
+          <t>facebook-login.messages.not-linked</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>You already linked a different Facebook account</t>
+          <t>This Facebook account is not linked. Log in another way and link it in Settings</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
+          <t>Tài khoản Facebook này chưa được liên kết. Hãy đăng nhập cách khác rồi liên kết trong Cài đặt</t>
         </is>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.unlinked</t>
+          <t>facebook-login.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Facebook unlinked</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Đã huỷ liên kết Facebook</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>facebook-link.messages.internal-server-error</t>
+          <t>facebook-link.messages.missing-token</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Facebook token is required</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thiếu thông tin đăng nhập Facebook</t>
         </is>
       </c>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.already-inactive</t>
+          <t>facebook-link.messages.invalid-token</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Session already inactive</t>
+          <t>Invalid Facebook token</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Phiên đã ngưng hoạt động</t>
+          <t>Thông tin đăng nhập Facebook không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.internal-server-error</t>
+          <t>facebook-link.messages.linked</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Facebook linked successfully</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Đã liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>logout.messages.success</t>
+          <t>facebook-link.messages.already-linked</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Logout successful</t>
+          <t>This Facebook account is already linked to your account</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất thành công</t>
+          <t>Tài khoản Facebook này đã được liên kết với bạn</t>
         </is>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.missing-refresh-token</t>
+          <t>facebook-link.messages.linked-to-other</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Missing refresh token cookie</t>
+          <t>This Facebook account is already linked to another account</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Thiếu cookie token làm mới</t>
+          <t>Tài khoản Facebook này đã được liên kết với tài khoản khác</t>
         </is>
       </c>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.mismatch-or-expired</t>
+          <t>facebook-link.messages.already-has-facebook</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Refresh token mismatch or expired</t>
+          <t>You already linked a different Facebook account</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Thiếu refresh token hoặc đã hết hạn</t>
+          <t>Bạn đã liên kết một tài khoản Facebook khác</t>
         </is>
       </c>
     </row>
     <row r="260" ht="36" customHeight="1">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>refresh-token.messages.success</t>
+          <t>facebook-link.messages.unlinked</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Token refreshed</t>
+          <t>Facebook unlinked</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Token đã làm mới</t>
+          <t>Đã huỷ liên kết Facebook</t>
         </is>
       </c>
     </row>
     <row r="261" ht="36" customHeight="1">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>register.messages.email-exists</t>
+          <t>facebook-link.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Email already exists</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Email đã tồn tại</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>register.messages.internal-server-error</t>
+          <t>logout.messages.already-inactive</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Session already inactive</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Phiên đã ngưng hoạt động</t>
         </is>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>register.messages.missing-fields</t>
+          <t>logout.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Username, password, gender, displayName and email are required</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>register.messages.success</t>
+          <t>logout.messages.success</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>User created successfully</t>
+          <t>Logout successful</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Người dùng được tạo thành công</t>
+          <t>Đăng xuất thành công</t>
         </is>
       </c>
     </row>
     <row r="265" ht="17" customHeight="1">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>register.messages.username-exists</t>
+          <t>refresh-token.messages.missing-refresh-token</t>
         </is>
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>Username already exists</t>
+          <t>Missing refresh token cookie</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>Tên người dùng đã tồn tại</t>
+          <t>Thiếu cookie token làm mới</t>
         </is>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.internal-server-error</t>
+          <t>refresh-token.messages.mismatch-or-expired</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Refresh token mismatch or expired</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Thiếu refresh token hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-or-expired-token</t>
+          <t>refresh-token.messages.success</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Invalid or expired reset password token</t>
+          <t>Token refreshed</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
+          <t>Token đã làm mới</t>
         </is>
       </c>
     </row>
     <row r="268" ht="18" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.invalid-user-id</t>
+          <t>register.messages.email-exists</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Invalid user id</t>
+          <t>Email already exists</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Email đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-id-or-token</t>
+          <t>register.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>ID and token are required</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>ID và token là bắt buộc</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.missing-userId-or-password</t>
+          <t>register.messages.missing-fields</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>UserId and password are required</t>
+          <t>Username, password, gender, displayName and email are required</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>UserId và mật khẩu là bắt buộc</t>
+          <t>Tên người dùng, mật khẩu, giới tính, tên hiển thị và email là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="271" ht="36" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.token-valid</t>
+          <t>register.messages.success</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Reset password token is valid</t>
+          <t>User created successfully</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Token đặt lại mật khẩu hợp lệ</t>
+          <t>Người dùng được tạo thành công</t>
         </is>
       </c>
     </row>
     <row r="272" ht="36" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>reset-password.messages.user-not-found</t>
+          <t>register.messages.username-exists</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>Username already exists</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Tên người dùng đã tồn tại</t>
         </is>
       </c>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>room.actions.start-room</t>
+          <t>reset-password.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Start room</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu chơi</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>room.actions.challenge</t>
+          <t>reset-password.messages.invalid-or-expired-token</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Invalid or expired reset password token</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Vào chơi</t>
+          <t>Token đặt lại mật khẩu không hợp lệ hoặc đã hết hạn</t>
         </is>
       </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>room.actions.leave-seat</t>
+          <t>reset-password.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Leave seat</t>
+          <t>Invalid user id</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Ra xem</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>room.actions.undo</t>
+          <t>reset-password.messages.missing-id-or-token</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Undo</t>
+          <t>ID and token are required</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Hoán tác</t>
+          <t>ID và token là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>room.actions.surrender</t>
+          <t>reset-password.messages.missing-userId-or-password</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Surrender</t>
+          <t>UserId and password are required</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Đầu hàng</t>
+          <t>UserId và mật khẩu là bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>room.actions.draw</t>
+          <t>reset-password.messages.token-valid</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Reset password token is valid</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Hòa</t>
+          <t>Token đặt lại mật khẩu hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-home</t>
+          <t>reset-password.messages.user-not-found</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Back to home</t>
+          <t>User not found</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Thoát phòng</t>
+          <t>Không tìm thấy người dùng</t>
         </is>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>room.actions.flip-board</t>
+          <t>room.actions.start-room</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Flip board</t>
+          <t>Start room</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Đảo chiều bàn cờ</t>
+          <t>Bắt đầu chơi</t>
         </is>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>room.actions.accept-draw</t>
+          <t>room.actions.challenge</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Chấp nhận</t>
+          <t>Vào chơi</t>
         </is>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>room.actions.reject-draw</t>
+          <t>room.actions.leave-seat</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Leave seat</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Từ chối</t>
+          <t>Ra xem</t>
         </is>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>room.actions.send-pm</t>
+          <t>room.actions.undo</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Send PM</t>
+          <t>Undo</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Hoán tác</t>
         </is>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>room.actions.view-history</t>
+          <t>room.actions.surrender</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Surrender</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử</t>
+          <t>Đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>room.actions.kick</t>
+          <t>room.actions.draw</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Hòa</t>
         </is>
       </c>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>room.actions.back-to-room</t>
+          <t>room.actions.back-home</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Back to room</t>
+          <t>Back to home</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Quay lại phòng chơi</t>
+          <t>Thoát phòng</t>
         </is>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>room.actions.chat</t>
+          <t>room.actions.flip-board</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Room chat</t>
+          <t>Flip board</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Phòng chat</t>
+          <t>Đảo chiều bàn cờ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-accepted</t>
+          <t>room.actions.accept-draw</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Opponent accepted the draw</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đồng ý hòa</t>
+          <t>Chấp nhận</t>
         </is>
       </c>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>room.messages.draw-rejected</t>
+          <t>room.actions.reject-draw</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Opponent rejected the draw</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Đối phương từ chối hòa</t>
+          <t>Từ chối</t>
         </is>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>room.messages.opponent-surrendered</t>
+          <t>room.actions.send-pm</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Opponent surrendered! You won!</t>
+          <t>Send PM</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-leave</t>
+          <t>room.actions.view-history</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to leave room?</t>
+          <t>History</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc muốn rời bàn chơi?</t>
+          <t>Lịch sử</t>
         </is>
       </c>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-surrender</t>
+          <t>room.actions.kick</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to surrender?</t>
+          <t>Kick</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
+          <t>Kick</t>
         </is>
       </c>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-draw</t>
+          <t>room.actions.back-to-room</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Are you sure you want to draw?</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Bạn có chắc chắn muốn hòa không?</t>
+          <t>Quay lại phòng chơi</t>
         </is>
       </c>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>room.messages.confirm-accept-draw</t>
+          <t>room.actions.chat</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Opponent has proposed a draw. Do you accept?</t>
+          <t>Room chat</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
+          <t>Phòng chat</t>
         </is>
       </c>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>room.messages.insufficient-amount</t>
+          <t>room.messages.draw-accepted</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to join this room</t>
+          <t>Opponent accepted the draw</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
+          <t>Đối phương đã đồng ý hòa</t>
         </is>
       </c>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>room.messages.will-leave-current-room</t>
+          <t>room.messages.draw-rejected</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>You are currently in another room. Joining this room will remove you from the current room</t>
+          <t>Opponent rejected the draw</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
+          <t>Đối phương từ chối hòa</t>
         </is>
       </c>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>room.messages.game-ended</t>
+          <t>room.messages.opponent-surrendered</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Game ended</t>
+          <t>Opponent surrendered! You won!</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Ván đấu đã kết thúc</t>
+          <t>Đối phương đã đầu hàng! Bạn thắng!</t>
         </is>
       </c>
     </row>
     <row r="298" ht="18" customHeight="1">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-win</t>
+          <t>room.messages.confirm-leave</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>You win</t>
+          <t>Are you sure you want to leave room?</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã chiến thắng</t>
+          <t>Bạn có chắc muốn rời bàn chơi?</t>
         </is>
       </c>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-lose</t>
+          <t>room.messages.confirm-surrender</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>You lose</t>
+          <t>Are you sure you want to surrender?</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Bạn đã thua</t>
+          <t>Bạn có chắc chắn muốn đầu hàng không?</t>
         </is>
       </c>
     </row>
     <row r="300" ht="18" customHeight="1">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-draw</t>
+          <t>room.messages.confirm-draw</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>The game is a draw</t>
+          <t>Are you sure you want to draw?</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Ván đấu hòa</t>
+          <t>Bạn có chắc chắn muốn hòa không?</t>
         </is>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-win-per-move-timeout</t>
+          <t>room.messages.confirm-accept-draw</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>You win — your opponent ran out of move time</t>
+          <t>Opponent has proposed a draw. Do you accept?</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Bạn thắng vì đối thủ hết giờ đi một nước</t>
+          <t>Đối phương đã chủ hòa, bạn có đồng ý không?</t>
         </is>
       </c>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>room.messages.you-lose-per-move-timeout</t>
+          <t>room.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>You lose — you ran out of move time</t>
+          <t>You do not have enough balance to join this room</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Bạn thua do hết giờ đi một nước</t>
+          <t>Bạn không đủ tiền để tham gia bàn chơi này</t>
         </is>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>room.messages.spectator-win-checkmate</t>
+          <t>room.messages.will-leave-current-room</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>{0} won by checkmate</t>
+          <t>You are currently in another room. Joining this room will remove you from the current room</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>{0} thắng do chiếu bí</t>
+          <t>Bạn đang ở trong một phòng khác. Tham gia phòng này sẽ loại bạn ra khỏi phòng hiện tại</t>
         </is>
       </c>
     </row>
     <row r="304" ht="18" customHeight="1">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>room.messages.spectator-win-stalemate</t>
+          <t>room.messages.game-ended</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>{0} won — opponent had no legal moves</t>
+          <t>Game ended</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>{0} thắng do đối thủ hết nước đi</t>
+          <t>Ván đấu đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>room.messages.spectator-win-timeout</t>
+          <t>room.messages.you-win</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>{0} won on time</t>
+          <t>You win</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>{0} thắng do đối thủ hết giờ</t>
+          <t>Bạn đã chiến thắng</t>
         </is>
       </c>
     </row>
     <row r="306" ht="90" customHeight="1">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>room.messages.spectator-win-per-move-timeout</t>
+          <t>room.messages.you-lose</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>{0} won — opponent ran out of move time</t>
+          <t>You lose</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>{0} thắng do đối thủ hết giờ đi một nước</t>
+          <t>Bạn đã thua</t>
         </is>
       </c>
     </row>
     <row r="307" ht="90" customHeight="1">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>room.messages.spectator-draw</t>
+          <t>room.messages.you-draw</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>The game ended in a draw</t>
+          <t>The game is a draw</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Ván đấu kết thúc với tỉ số hòa</t>
+          <t>Ván đấu hòa</t>
         </is>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>room.messages.back-to-room</t>
+          <t>room.messages.you-win-per-move-timeout</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Back to room</t>
+          <t>You win — your opponent ran out of move time</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Quay lại phòng</t>
+          <t>Bạn thắng vì đối thủ hết giờ đi một nước</t>
         </is>
       </c>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>room.messages.auto-back-countdown</t>
+          <t>room.messages.you-lose-per-move-timeout</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>{0}. Press the back button to return to the room. You will be automatically returned in {1}s</t>
+          <t>You lose — you ran out of move time</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>{0}. Bấm nút quay lại để quay lại room. Bạn sẽ tự động quay lại trong {1}s</t>
+          <t>Bạn thua do hết giờ đi một nước</t>
         </is>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>room.notifications.joined</t>
+          <t>room.messages.spectator-win-checkmate</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>{0} joined the room</t>
+          <t>{0} won by checkmate</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>{0} đã vào phòng</t>
+          <t>{0} thắng do chiếu bí</t>
         </is>
       </c>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>room.notifications.left</t>
+          <t>room.messages.spectator-win-stalemate</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>{0} left the room</t>
+          <t>{0} won — opponent had no legal moves</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>{0} đã rời phòng</t>
+          <t>{0} thắng do đối thủ hết nước đi</t>
         </is>
       </c>
     </row>
     <row r="312" ht="18" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>room.settings.title</t>
+          <t>room.messages.spectator-win-timeout</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Room Settings</t>
+          <t>{0} won on time</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Cài đặt phòng</t>
+          <t>{0} thắng do đối thủ hết giờ</t>
         </is>
       </c>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>room.settings.room-name</t>
+          <t>room.messages.spectator-win-per-move-timeout</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Room name</t>
+          <t>{0} won — opponent ran out of move time</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng</t>
+          <t>{0} thắng do đối thủ hết giờ đi một nước</t>
         </is>
       </c>
     </row>
     <row r="314" ht="18" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>room.settings.players</t>
+          <t>room.messages.spectator-draw</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Spectators</t>
+          <t>The game ended in a draw</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Người xem</t>
+          <t>Ván đấu kết thúc với tỉ số hòa</t>
         </is>
       </c>
     </row>
     <row r="315" ht="54" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>room.settings.save</t>
+          <t>room.messages.back-to-room</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Back to room</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Quay lại phòng</t>
         </is>
       </c>
     </row>
     <row r="316" ht="18" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>room-invite.messages.title</t>
+          <t>room.messages.auto-back-countdown</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Room Invitation</t>
+          <t>{0}. Press the back button to return to the room. You will be automatically returned in {1}s</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Lời mời vào phòng</t>
+          <t>{0}. Bấm nút quay lại để quay lại room. Bạn sẽ tự động quay lại trong {1}s</t>
         </is>
       </c>
     </row>
     <row r="317" ht="90" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.success</t>
+          <t>room.notifications.joined</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Game started successfully</t>
+          <t>{0} joined the room</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu trò chơi thành công</t>
+          <t>{0} đã vào phòng</t>
         </is>
       </c>
     </row>
     <row r="318" ht="18" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.internal-server-error</t>
+          <t>room.notifications.left</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Internal server error while starting game</t>
+          <t>{0} left the room</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
+          <t>{0} đã rời phòng</t>
         </is>
       </c>
     </row>
     <row r="319" ht="36" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-room-id</t>
+          <t>room.settings.title</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Field 'id' is required and must be a positive integer</t>
+          <t>Room Settings</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
+          <t>Cài đặt phòng</t>
         </is>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.invalid-difficulty</t>
+          <t>room.settings.room-name</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Bot difficulty must be between 1 and 5</t>
+          <t>Room name</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Độ khó của bot phải từ 1 đến 5</t>
+          <t>Tên phòng</t>
         </is>
       </c>
     </row>
     <row r="321" ht="72" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.room-not-found</t>
+          <t>room.settings.players</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Spectators</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Người xem</t>
         </is>
       </c>
     </row>
     <row r="322" ht="18" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.forbidden</t>
+          <t>room.settings.save</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Only the room host can start the game</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="323" ht="54" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.insufficient-amount</t>
+          <t>room-invite.messages.title</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>You do not have enough balance to start a game with this bet</t>
+          <t>Room Invitation</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Bạn không còn đủ amount để start room</t>
+          <t>Lời mời vào phòng</t>
         </is>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>start-game.messages.requester-must-pick-team</t>
+          <t>start-game.messages.success</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>You must select a team before starting a game with bot</t>
+          <t>Game started successfully</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
+          <t>Bắt đầu trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="325" ht="72" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.success</t>
+          <t>start-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Room updated successfully</t>
+          <t>Internal server error while starting game</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật phòng thành công</t>
+          <t>Lỗi máy chủ nội bộ khi bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="326" ht="18" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.internal-server-error</t>
+          <t>start-game.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Field 'id' is required and must be a positive integer</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Trường 'id' là bắt buộc và phải là số nguyên dương</t>
         </is>
       </c>
     </row>
     <row r="327" ht="90" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-room-id</t>
+          <t>start-game.messages.invalid-difficulty</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Invalid room ID</t>
+          <t>Bot difficulty must be between 1 and 5</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>ID phòng không hợp lệ</t>
+          <t>Độ khó của bot phải từ 1 đến 5</t>
         </is>
       </c>
     </row>
     <row r="328" ht="18" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-time-limit</t>
+          <t>start-game.messages.room-not-found</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Invalid time limit</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Thời gian không hợp lệ</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="329" ht="72" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-time-increment</t>
+          <t>start-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Invalid bonus per move</t>
+          <t>Only the room host can start the game</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>Thời gian cộng mỗi nước không hợp lệ</t>
+          <t>Chỉ chủ phòng mới có thể bắt đầu trò chơi</t>
         </is>
       </c>
     </row>
     <row r="330" ht="54" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.invalid-time-per-move</t>
+          <t>start-game.messages.insufficient-amount</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Invalid time per move</t>
+          <t>You do not have enough balance to start a game with this bet</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Thời gian mỗi nước không hợp lệ</t>
+          <t>Bạn không còn đủ amount để start room</t>
         </is>
       </c>
     </row>
     <row r="331" ht="54" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.name-required</t>
+          <t>start-game.messages.requester-must-pick-team</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Room name is required</t>
+          <t>You must select a team before starting a game with bot</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Tên phòng không được để trống</t>
+          <t>Bạn phải chọn team trước khi bắt đầu trò chơi với bot</t>
         </is>
       </c>
     </row>
     <row r="332" ht="54" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.room-not-found</t>
+          <t>update-room.messages.success</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Room not found</t>
+          <t>Room updated successfully</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng</t>
+          <t>Cập nhật phòng thành công</t>
         </is>
       </c>
     </row>
     <row r="333" ht="90" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>update-room.messages.forbidden</t>
+          <t>update-room.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>You are not the host of this room</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải chủ phòng</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="334" ht="54" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.invalid-game-id</t>
+          <t>update-room.messages.invalid-room-id</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Invalid room ID</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>ID phòng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="335" ht="36" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-not-found</t>
+          <t>update-room.messages.invalid-time-limit</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Invalid time limit</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Thời gian không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.forbidden</t>
+          <t>update-room.messages.invalid-time-increment</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>Invalid bonus per move</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Bạn không có trong phòng này</t>
+          <t>Thời gian cộng mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="337" ht="36" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-history-not-found</t>
+          <t>update-room.messages.invalid-time-per-move</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>Invalid time per move</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Thời gian mỗi nước không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="338" ht="36" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.game-already-finished</t>
+          <t>update-room.messages.name-required</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>Room name is required</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>Tên phòng không được để trống</t>
         </is>
       </c>
     </row>
     <row r="339" ht="72" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.success</t>
+          <t>update-room.messages.room-not-found</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>Draw game successfully</t>
+          <t>Room not found</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Hòa cờ thành công</t>
+          <t>Không tìm thấy phòng</t>
         </is>
       </c>
     </row>
     <row r="340" ht="54" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>draw-game.messages.internal-server-error</t>
+          <t>update-room.messages.forbidden</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You are not the host of this room</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bạn không phải chủ phòng</t>
         </is>
       </c>
     </row>
     <row r="341" ht="54" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.game-already-finished</t>
+          <t>draw-game.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Game is already finished</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Trò chơi đã kết thúc</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="342" ht="90" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.game-history-not-found</t>
+          <t>draw-game.messages.game-not-found</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>Game history not found</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy lịch sử trò chơi</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="343" ht="54" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.game-not-found</t>
+          <t>draw-game.messages.forbidden</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Bạn không có trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.internal-server-error</t>
+          <t>draw-game.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-game-id</t>
+          <t>draw-game.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="346" ht="36" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.invalid-surrender-player</t>
+          <t>draw-game.messages.success</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>You are not a player in this game</t>
+          <t>Draw game successfully</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>Hòa cờ thành công</t>
         </is>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.opponent-not-found</t>
+          <t>draw-game.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Opponent not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy đối thủ</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>surrender.messages.success</t>
+          <t>surrender.messages.game-already-finished</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Surrendered</t>
+          <t>Game is already finished</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Đã đầu hàng</t>
+          <t>Trò chơi đã kết thúc</t>
         </is>
       </c>
     </row>
     <row r="349" ht="36" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.invalid-game-id</t>
+          <t>surrender.messages.game-history-not-found</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Invalid game ID</t>
+          <t>Game history not found</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>ID trò chơi không hợp lệ</t>
+          <t>Không tìm thấy lịch sử trò chơi</t>
         </is>
       </c>
     </row>
     <row r="350" ht="18" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.unauthorized</t>
+          <t>surrender.messages.game-not-found</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>Unauthorized</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Không được phép truy cập</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="351" ht="36" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.game-not-found</t>
+          <t>surrender.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>Game not found</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Không tìm thấy trò chơi</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="352" ht="18" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-game</t>
+          <t>surrender.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>You are not part of this game</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Bạn không phải là người chơi trong trò chơi này</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="353" ht="18" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.not-in-room</t>
+          <t>surrender.messages.invalid-surrender-player</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>You are not in this room</t>
+          <t>You are not a player in this game</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Bạn không trong phòng này</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="354" ht="18" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.pve-only</t>
+          <t>surrender.messages.opponent-not-found</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Undo is only available in PvE rooms</t>
+          <t>Opponent not found</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Hoàn tác chỉ khả dụng trong phòng PvE</t>
+          <t>Không tìm thấy đối thủ</t>
         </is>
       </c>
     </row>
     <row r="355" ht="18" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.spectator-cannot-undo</t>
+          <t>surrender.messages.success</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Spectators cannot undo moves</t>
+          <t>Surrendered</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Người xem không thể hoàn tác nước đi</t>
+          <t>Đã đầu hàng</t>
         </is>
       </c>
     </row>
     <row r="356" ht="18" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.no-moves</t>
+          <t>undo.messages.invalid-game-id</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>No moves to undo</t>
+          <t>Invalid game ID</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Không có nước đi để hoàn tác</t>
+          <t>ID trò chơi không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="357" ht="17" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.delete-failed</t>
+          <t>undo.messages.unauthorized</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Failed to undo move</t>
+          <t>Unauthorized</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Không thể hoàn tác nước đi</t>
+          <t>Không được phép truy cập</t>
         </is>
       </c>
     </row>
     <row r="358" ht="18" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.undo-limit-exceeded</t>
+          <t>undo.messages.game-not-found</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Maximum 3 undo per game exceeded</t>
+          <t>Game not found</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
+          <t>Không tìm thấy trò chơi</t>
         </is>
       </c>
     </row>
     <row r="359" ht="18" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.success</t>
+          <t>undo.messages.not-in-game</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>Move undone successfully</t>
+          <t>You are not part of this game</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Hoàn tác nước đi thành công</t>
+          <t>Bạn không phải là người chơi trong trò chơi này</t>
         </is>
       </c>
     </row>
     <row r="360" ht="18" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>undo.messages.internal-server-error</t>
+          <t>undo.messages.not-in-room</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>Internal server error</t>
+          <t>You are not in this room</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Lỗi máy chủ nội bộ</t>
+          <t>Bạn không trong phòng này</t>
         </is>
       </c>
     </row>
     <row r="361" ht="18" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.invalid-user-id</t>
+          <t>undo.messages.pve-only</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>Invalid user ID</t>
+          <t>Undo is only available in PvE rooms</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>ID người dùng không hợp lệ</t>
+          <t>Hoàn tác chỉ khả dụng trong phòng PvE</t>
         </is>
       </c>
     </row>
     <row r="362" ht="18" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>player-history.messages.success</t>
+          <t>undo.messages.spectator-cannot-undo</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>Fetch game history successfully</t>
+          <t>Spectators cannot undo moves</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Lấy lịch sử trò chơi thành công</t>
+          <t>Người xem không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="363" ht="18" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>validate-token.messages.success</t>
+          <t>undo.messages.no-moves</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>Token is valid</t>
+          <t>No moves to undo</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Token hợp lệ</t>
+          <t>Không có nước đi để hoàn tác</t>
         </is>
       </c>
     </row>
     <row r="364" ht="17" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>guide.section.objective</t>
+          <t>undo.messages.delete-failed</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Objective of the game</t>
+          <t>Failed to undo move</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu của trò chơi</t>
+          <t>Không thể hoàn tác nước đi</t>
         </is>
       </c>
     </row>
     <row r="365" ht="17" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>guide.section.pieces</t>
+          <t>undo.messages.undo-limit-exceeded</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>Pieces</t>
+          <t>Maximum 3 undo per game exceeded</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Quân cờ</t>
+          <t>Đã đạt tối đa 3 lần hoàn tác trong trò chơi</t>
         </is>
       </c>
     </row>
     <row r="366" ht="17" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>guide.section.moving-pieces</t>
+          <t>undo.messages.success</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Moving pieces</t>
+          <t>Move undone successfully</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Đi quân</t>
+          <t>Hoàn tác nước đi thành công</t>
         </is>
       </c>
     </row>
     <row r="367" ht="17" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>guide.section.capturing</t>
+          <t>undo.messages.internal-server-error</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>Capturing</t>
+          <t>Internal server error</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Bắt quân</t>
+          <t>Lỗi máy chủ nội bộ</t>
         </is>
       </c>
     </row>
     <row r="368" ht="17" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>guide.section.check</t>
+          <t>player-history.messages.invalid-user-id</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Invalid user ID</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Chiếu tướng</t>
+          <t>ID người dùng không hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="369" ht="17" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>guide.section.result</t>
+          <t>player-history.messages.success</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Fetch game history successfully</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Kết quả</t>
+          <t>Lấy lịch sử trò chơi thành công</t>
         </is>
       </c>
     </row>
     <row r="370" ht="17" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>guide.table.piece</t>
+          <t>validate-token.messages.success</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Piece</t>
+          <t>Token is valid</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Quân</t>
+          <t>Token hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="371" ht="17" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>guide.table.symbol</t>
+          <t>guide.section.objective</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Symbol</t>
+          <t>Objective of the game</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Ký hiệu</t>
+          <t>Mục tiêu của trò chơi</t>
         </is>
       </c>
     </row>
     <row r="372" ht="17" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>guide.table.quantity</t>
+          <t>guide.section.pieces</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Pieces</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Số lượng</t>
+          <t>Quân cờ</t>
         </is>
       </c>
     </row>
     <row r="373" ht="17" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>guide.objective.paragraph1</t>
+          <t>guide.section.moving-pieces</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
+          <t>Moving pieces</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
+          <t>Đi quân</t>
         </is>
       </c>
     </row>
     <row r="374" ht="17" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>guide.pieces.paragraph1</t>
+          <t>guide.section.capturing</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
+          <t>Capturing</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
+          <t>Bắt quân</t>
         </is>
       </c>
     </row>
     <row r="375" ht="17" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.general</t>
+          <t>guide.section.check</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Chiếu tướng</t>
         </is>
       </c>
     </row>
     <row r="376" ht="17" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.advisor</t>
+          <t>guide.section.result</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Kết quả</t>
         </is>
       </c>
     </row>
     <row r="377" ht="17" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.elephant</t>
+          <t>guide.table.piece</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Piece</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Quân</t>
         </is>
       </c>
     </row>
     <row r="378" ht="17" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.chariot</t>
+          <t>guide.table.symbol</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Symbol</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Ký hiệu</t>
         </is>
       </c>
     </row>
     <row r="379" ht="17" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.horse</t>
+          <t>guide.table.quantity</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Số lượng</t>
         </is>
       </c>
     </row>
     <row r="380" ht="17" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.cannon</t>
+          <t>guide.objective.paragraph1</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>A match is played between two players: one controls the Red pieces, and the other controls the Black pieces. The objective of each player is to use their pieces on the board to &lt;b&gt;checkmate&lt;/b&gt; the opponent's General, and win the game.</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Ván cờ được tiến hành giữa 2 đấu thủ, một người cầm Quân Đỏ, một người cầm Quân Đen. Mục đích của mỗi đấu thủ là tìm mọi cách sử dụng các quân trên bàn cờ để &lt;b&gt;chiếu bí Tướng&lt;/b&gt; của đối phương, giành thắng lợi.</t>
         </is>
       </c>
     </row>
     <row r="381" ht="17" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>guide.piece.soldier</t>
+          <t>guide.pieces.paragraph1</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>At the start of each game, there must be 32 pieces in total, consisting of &lt;b&gt;7 piece types&lt;/b&gt; split evenly between both sides: 16 Red pieces and 16 Black pieces. The 7 piece types with their symbols and quantities are as follows:</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Mỗi ván cờ lúc bắt đầu phải có đủ 32 quân, gồm 7 loại chia đều cho mỗi bên gồm 16 quân Đỏ và 16 quân Đen. &lt;b&gt;7 loại quân&lt;/b&gt; có ký hiệu và số lượng như sau:</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>guide.moving-pieces.paragraph1</t>
+          <t>guide.piece.general</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>guide.general.paragraph1</t>
+          <t>guide.piece.advisor</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Tướng</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>guide.general.paragraph2</t>
+          <t>guide.piece.elephant</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph1</t>
+          <t>guide.piece.chariot</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Advisor</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Sĩ</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>guide.advisor.paragraph2</t>
+          <t>guide.piece.horse</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph1</t>
+          <t>guide.piece.cannon</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Tượng</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>guide.elephant.paragraph2</t>
+          <t>guide.piece.soldier</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph1</t>
+          <t>guide.moving-pieces.paragraph1</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>On each turn, each side may move only one of its own pieces according to the rules. The movement rules are as follows:</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Xe</t>
+          <t>Mỗi nước đi, mỗi bên chỉ được di chuyển quân của mình theo đúng quy định. Quy định di chuyển của các quân như sau:</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>guide.chariot.paragraph2</t>
+          <t>guide.general.paragraph1</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
+          <t>Tướng</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph1</t>
+          <t>guide.general.paragraph2</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Moves one step &lt;b&gt;horizontally or vertically&lt;/b&gt; within the palace. The two Generals may not face each other directly on the same file. If they are facing each other, there must be at least one piece of either side placed between them.</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mã</t>
+          <t>Mỗi nước được đi một bước &lt;b&gt;ngang hoặc dọc&lt;/b&gt; tùy ý trong cung Tướng. Hai tướng của 2 bên không được đối mặt nhau trực tiếp trên cùng một đường thẳng. Nếu đối mặt, bắt buộc phải có quân của bất kỳ bên nào đứng che mặt.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>guide.horse.paragraph2</t>
+          <t>guide.advisor.paragraph1</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
+          <t>Advisor</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
+          <t>Sĩ</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph1</t>
+          <t>guide.advisor.paragraph2</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Cannon</t>
+          <t>Moves one step &lt;b&gt;diagonally&lt;/b&gt; within the palace.</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Pháo</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo một bước&lt;/b&gt; trong cung Tướng.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>guide.cannon.paragraph2</t>
+          <t>guide.elephant.paragraph1</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
+          <t>Tượng</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph1</t>
+          <t>guide.elephant.paragraph2</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Moves &lt;b&gt;two steps diagonally&lt;/b&gt; on its own side of the board and may not cross the river. If there is another piece on the midpoint of that diagonal path, the Elephant is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Tốt</t>
+          <t>Mỗi nước &lt;b&gt;đi chéo hai bước&lt;/b&gt; tại trận địa bên mình, không được qua sông. Nếu ở giữa đường chéo đó có quân khác đứng thì quân Tượng bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>guide.soldier.paragraph2</t>
+          <t>guide.chariot.paragraph1</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
+          <t>Xe</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph1</t>
+          <t>guide.chariot.paragraph2</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; with no limit on distance, as long as no piece blocks the path.</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
+          <t>Mỗi nước được &lt;b&gt;đi dọc hoặc đi ngang&lt;/b&gt;, không hạn chế số bước đi nếu không có quân khác cản đường.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph2</t>
+          <t>guide.horse.paragraph1</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
+          <t>Mã</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>guide.capturing.paragraph3</t>
+          <t>guide.horse.paragraph2</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
+          <t>Moves in an &lt;b&gt;L-shape&lt;/b&gt; (one step orthogonally then one step diagonally outward). If the adjacent orthogonal point is occupied by any piece, the Horse is blocked and cannot move.</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
+          <t>Đi theo &lt;b&gt;đường chéo hình chữ nhật&lt;/b&gt; của hai ô vuông liền nhau. Nếu giao điểm liền kề bước thẳng dọc ngang có một quân khác đứng thì Mã bị cản, không đi được.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>guide.check.paragraph1</t>
+          <t>guide.cannon.paragraph1</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
+          <t>Cannon</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
+          <t>Pháo</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>guide.check.paragraph2</t>
+          <t>guide.cannon.paragraph2</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
+          <t>Moves &lt;b&gt;horizontally or vertically&lt;/b&gt; like a Chariot when not capturing. To capture, it must &lt;b&gt;jump over exactly one piece&lt;/b&gt; to reach its target. If there are zero or more than one pieces between the Cannon and the target, it cannot capture.</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
+          <t>Đi ngang hoặc dọc giống Xe khi không bắt quân. Để bắt quân, nó phải &lt;b&gt;nhảy qua đúng một quân khác&lt;/b&gt; để đến mục tiêu. Nếu không có hoặc có nhiều hơn một quân giữa Pháo và mục tiêu, nó không thể bắt quân.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>guide.check.paragraph3</t>
+          <t>guide.soldier.paragraph1</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Move the General to another position to escape check</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
+          <t>Tốt</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>guide.check.paragraph4</t>
+          <t>guide.soldier.paragraph2</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Capture the checking piece</t>
+          <t>Moves &lt;b&gt;one step&lt;/b&gt; each turn. Before crossing the river, it can only move forward. After crossing the river, it may move &lt;b&gt;forward or sideways&lt;/b&gt;, but never backward.</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Bắt quân đang chiếu</t>
+          <t>Mỗi nước đi &lt;b&gt;một bước&lt;/b&gt;. Khi chưa qua sông, Tốt chỉ được tiến. Khi Tốt đã qua sông được quyền &lt;b&gt;đi tiến và đi ngang&lt;/b&gt;, không được phép lùi.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>guide.check.paragraph5</t>
+          <t>guide.capturing.paragraph1</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Block the checking line with another piece to protect the General</t>
+          <t>When a piece moves to an intersection occupied by an opponent's piece, it may &lt;b&gt;capture that piece&lt;/b&gt; and occupy its position.</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
+          <t>Khi một quân đi tới một giao điểm khác đã có quân đối phương đứng thì được quyền &lt;b&gt;bắt quân đó&lt;/b&gt;, đồng thời chiếm giữ vị trí quân bị bắt.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>guide.check.paragraph6</t>
+          <t>guide.capturing.paragraph2</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
+          <t>You may not capture your own pieces. You may sacrifice your own pieces to be captured by the opponent, &lt;b&gt;except for the General&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
+          <t>Không được bắt quân bên mình. Được phép cho đối phương bắt đầu quân mình chủ động hiến mình cho đối phương, &lt;b&gt;trừ Tướng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>guide.result.paragraph1</t>
+          <t>guide.capturing.paragraph3</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
+          <t>A captured piece is removed from the board. &lt;b&gt;Chasing one piece for more than 6 consecutive moves is not allowed&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
+          <t>Quân bị bắt phải bị loại và bị nhấc ra khỏi bàn cờ. &lt;b&gt;Không được đuổi 1 quân quá 6 nước cờ liên tiếp&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>guide.result.paragraph2</t>
+          <t>guide.check.paragraph1</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>If a player makes a move that threatens to capture the opponent's General on the next move (by the same piece or another piece), it is called a &lt;b&gt;Check&lt;/b&gt;. The checked side must respond to avoid check. Otherwise, that side loses</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Nếu người chơi thực hiện một nước đi đe dọa bắt Tướng của đối phương ở nước đi tiếp theo (bằng chính quân cờ đó hoặc một quân cờ khác), thì đó được gọi là &lt;b&gt;Chiếu&lt;/b&gt;. Bên bị chiếu phải đáp trả để tránh bị chiếu. Nếu không sẽ bị xử thua</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>guide.result.paragraph3</t>
+          <t>guide.check.paragraph2</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
+          <t>When the General is checked from any direction (including from behind), the checked side may respond in one of the following ways:</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
+          <t>Tướng bị chiếu từ cả bốn hướng (bị chiếu cả từ phía sau) có thể ứng phó với nước chiếu tướng bằng một trong các cách sau:</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>guide.result.paragraph4</t>
+          <t>guide.check.paragraph3</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>Move the General to another position to escape check</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Di chuyển tướng sang vị trí khác để tránh nước chiếu</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>guide.result.paragraph5</t>
+          <t>guide.check.paragraph4</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Within 50 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
+          <t>Capture the checking piece</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Trong vòng 50 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
+          <t>Bắt quân đang chiếu</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>extra-money.title</t>
+          <t>guide.check.paragraph5</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Daily tasks</t>
+          <t>Block the checking line with another piece to protect the General</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Kiếm tiền</t>
+          <t>Dùng quân khác cản quân chiếu, đi quân che đỡ cho tướng</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>extra-money.tab.lucky-wheel</t>
+          <t>guide.check.paragraph6</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Lucky Wheel</t>
+          <t>Repeatedly checking for more than 6 consecutive moves is not allowed</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Vòng Quay May Mắn</t>
+          <t>Không được chiếu tướng quá 6 nước cờ liên tiếp</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>extra-money.tab.bonus-coin</t>
+          <t>guide.result.paragraph1</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Bonus Coin</t>
+          <t>When one side gives Check and the other side has no legal way to protect the General, it is called a &lt;b&gt;Checkmate&lt;/b&gt;. The side that delivers Checkmate wins.</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Xu Thưởng</t>
+          <t>Khi một bên chiếu Tướng mà bên còn lại không thể làm gì để bảo vệ Tướng thì được gọi là &lt;b&gt;Chiếu Hết&lt;/b&gt;, bên thực hiện được Chiếu Hết sẽ giành chiến thắng.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>extra-money.tab.daily-bonus</t>
+          <t>guide.result.paragraph2</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Daily Bonus</t>
+          <t>If a player runs out of time for a single move (for example: 90s) without moving, the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Thưởng hàng ngày</t>
+          <t>Khi hết thời gian một nước đi (ví dụ: 90s) mà vẫn chưa di chuyển quân thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.subtitle</t>
+          <t>guide.result.paragraph3</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Watch a short video to earn free coin</t>
+          <t>If a player runs out of total game time (for example: 5 minutes or 10 minutes), the other side is awarded a &lt;b&gt;win&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Xem video ngắn để nhận xu miễn phí</t>
+          <t>Khi một bên hết thời gian ván đấu (ví dụ: 5 phút, 10 phút) thì bên còn lại sẽ được &lt;b&gt;xử Thắng&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.next-in</t>
+          <t>guide.result.paragraph4</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Next in:</t>
+          <t>If both sides have no pieces that have crossed the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;. If one side still has pieces across the river but runs out of time, while the other side still has time but has no pieces across the river, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Lượt kế tiếp:</t>
+          <t>Khi cả 2 bên đều không còn quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;. Khi một bên còn quân qua sông nhưng cạn thời gian, một bên còn thời gian nhưng hết quân qua sông, ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.collect</t>
+          <t>guide.result.paragraph5</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Collect</t>
+          <t>Within 50 moves, if there is no capture and no Soldier advances by one square, the game is declared a &lt;b&gt;draw&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Thu thập</t>
+          <t>Trong vòng 50 nước nếu không phát sinh nước bắt quân, Tốt không tiến 1 ô thì ván đấu sẽ được &lt;b&gt;xử Hòa&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>extra-money.bonus-coin.watch-video</t>
+          <t>extra-money.title</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Watch video</t>
+          <t>Daily tasks</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Xem video</t>
+          <t>Kiếm tiền</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.subtitle</t>
+          <t>extra-money.tab.lucky-wheel</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Login 7 days in a row to earn 4000 coin</t>
+          <t>Lucky Wheel</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
+          <t>Vòng Quay May Mắn</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>extra-money.daily-bonus.day</t>
+          <t>extra-money.tab.bonus-coin</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Bonus Coin</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Ngày</t>
+          <t>Xu Thưởng</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.loading</t>
+          <t>extra-money.tab.daily-bonus</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Loading ad...</t>
+          <t>Daily Bonus</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Đang tải quảng cáo...</t>
+          <t>Thưởng hàng ngày</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.error</t>
+          <t>extra-money.bonus-coin.subtitle</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Could not load the ad. Please try again.</t>
+          <t>Watch a short video to earn free coin</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
+          <t>Xem video ngắn để nhận xu miễn phí</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.retry</t>
+          <t>extra-money.bonus-coin.next-in</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Try again</t>
+          <t>Next in:</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Lượt kế tiếp:</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>extra-money.reward-ad.close</t>
+          <t>extra-money.bonus-coin.collect</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Collect</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Thu thập</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>profile.button.save</t>
+          <t>extra-money.bonus-coin.watch-video</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Watch video</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Lưu</t>
+          <t>Xem video</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>profile.button.cancel</t>
+          <t>extra-money.daily-bonus.subtitle</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Login 7 days in a row to earn 4000 coin</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Huỷ</t>
+          <t>Đăng nhập 7 ngày liên tiếp để nhận 4000 xu</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>change-password.title</t>
+          <t>extra-money.daily-bonus.day</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Ngày</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>change-password.current.label</t>
+          <t>extra-money.reward-ad.loading</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Current password</t>
+          <t>Loading ad...</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại</t>
+          <t>Đang tải quảng cáo...</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>change-password.current.placeholder</t>
+          <t>extra-money.reward-ad.error</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Enter current password</t>
+          <t>Could not load the ad. Please try again.</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu hiện tại</t>
+          <t>Không tải được quảng cáo. Vui lòng thử lại.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>change-password.new.label</t>
+          <t>extra-money.reward-ad.retry</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Try again</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Mật khẩu mới</t>
+          <t>Thử lại</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>change-password.new.placeholder</t>
+          <t>extra-money.reward-ad.close</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Enter new password</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Nhập mật khẩu mới</t>
+          <t>Đóng</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>change-password.confirm.label</t>
+          <t>profile.button.save</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Confirm new password</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Xác nhận mật khẩu mới</t>
+          <t>Lưu</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>change-password.confirm.placeholder</t>
+          <t>profile.button.cancel</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Re-enter new password</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Nhập lại mật khẩu mới</t>
+          <t>Huỷ</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>change-password.confirm.mismatch</t>
+          <t>change-password.title</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Passwords do not match</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Mật khẩu xác nhận không khớp</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>change-password.show</t>
+          <t>change-password.current.label</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Show password</t>
+          <t>Current password</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Hiện mật khẩu</t>
+          <t>Mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>change-password.hide</t>
+          <t>change-password.current.placeholder</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Hide password</t>
+          <t>Enter current password</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Ẩn mật khẩu</t>
+          <t>Nhập mật khẩu hiện tại</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>change-password.submit</t>
+          <t>change-password.new.label</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>New password</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu</t>
+          <t>Mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>change-password.submitting</t>
+          <t>change-password.new.placeholder</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Changing...</t>
+          <t>Enter new password</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Đang đổi...</t>
+          <t>Nhập mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>change-password.messages.success</t>
+          <t>change-password.confirm.label</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Password changed successfully</t>
+          <t>Confirm new password</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu thành công</t>
+          <t>Xác nhận mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>change-password.messages.missing-fields</t>
+          <t>change-password.confirm.placeholder</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Please fill in all fields</t>
+          <t>Re-enter new password</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Vui lòng nhập đầy đủ thông tin</t>
+          <t>Nhập lại mật khẩu mới</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>change-password.messages.weak-password</t>
+          <t>change-password.confirm.mismatch</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>New password does not meet the requirements</t>
+          <t>Passwords do not match</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Mật khẩu mới không đạt yêu cầu</t>
+          <t>Mật khẩu xác nhận không khớp</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>change-password.messages.same-as-current</t>
+          <t>change-password.show</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>New password must be different from the current one</t>
+          <t>Show password</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
+          <t>Hiện mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>change-password.messages.incorrect-current-password</t>
+          <t>change-password.hide</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Current password is incorrect</t>
+          <t>Hide password</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Mật khẩu hiện tại không đúng</t>
+          <t>Ẩn mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>change-password.messages.user-not-found</t>
+          <t>change-password.submit</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>User not found</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Không tìm thấy người dùng</t>
+          <t>Đổi mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>change-password.messages.unauthorized</t>
+          <t>change-password.submitting</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Session expired. Please sign in again.</t>
+          <t>Changing...</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
+          <t>Đang đổi...</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
+          <t>change-password.messages.success</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Password changed successfully</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu thành công</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>change-password.messages.missing-fields</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Please fill in all fields</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập đầy đủ thông tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>change-password.messages.weak-password</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>New password does not meet the requirements</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới không đạt yêu cầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>change-password.messages.same-as-current</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>New password must be different from the current one</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới phải khác mật khẩu hiện tại</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>change-password.messages.incorrect-current-password</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Current password is incorrect</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Mật khẩu hiện tại không đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>change-password.messages.user-not-found</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>User not found</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Không tìm thấy người dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>change-password.messages.unauthorized</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Session expired. Please sign in again.</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Phiên đăng nhập đã hết hạn. Vui lòng đăng nhập lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
           <t>change-password.messages.internal-server-error</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
+      <c r="B453" t="inlineStr">
         <is>
           <t>Something went wrong. Please try again.</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr">
+      <c r="C453" t="inlineStr">
         <is>
           <t>Đã có lỗi xảy ra. Vui lòng thử lại.</t>
         </is>
       </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr"/>
-      <c r="B447" t="inlineStr"/>
-      <c r="C447" t="inlineStr"/>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr"/>
-      <c r="B448" t="inlineStr"/>
-      <c r="C448" t="inlineStr"/>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr"/>
-      <c r="B449" t="inlineStr"/>
-      <c r="C449" t="inlineStr"/>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr"/>
-      <c r="B450" t="inlineStr"/>
-      <c r="C450" t="inlineStr"/>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr"/>
-      <c r="B451" t="inlineStr"/>
-      <c r="C451" t="inlineStr"/>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr"/>
-      <c r="B452" t="inlineStr"/>
-      <c r="C452" t="inlineStr"/>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr"/>
-      <c r="B453" t="inlineStr"/>
-      <c r="C453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr"/>
@@ -8009,6 +8093,41 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr"/>
       <c r="C465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr"/>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr"/>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr"/>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr"/>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr"/>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr"/>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr"/>
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
